--- a/AQI.xlsx
+++ b/AQI.xlsx
@@ -3,10 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet_2025-03-19" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet_2025-07-07" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet_2025-11-26" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet_2025-11-27" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet_2026-01-29" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet_2026-01-30" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet_2026-01-31" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet_2026-02-02" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet_2026-03-17" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet_2026-04-14" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet_2026-04-15" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet_2026-04-21" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet_2026-04-22" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet_2026-05-05" sheetId="11" r:id="rId11"/>
+    <sheet name="Sheet_2026-05-06" sheetId="12" r:id="rId12"/>
+    <sheet name="Sheet_2026-05-13" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet_2026-05-16" sheetId="14" r:id="rId14"/>
   </sheets>
 </workbook>
 </file>
@@ -35,8 +45,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -400,7 +414,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>_x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000_</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,134 +442,4538 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>00</v>
+        <v>51262</v>
       </c>
       <c r="B2" t="str">
-        <v>19/3/2025, 12:07:57 pm</v>
+        <v>4/22/2026, 12:10:09 PM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>00</v>
+        <v>030</v>
       </c>
       <c r="B3" t="str">
-        <v>19/3/2025, 12:08:57 pm</v>
+        <v>4/22/2026, 12:11:09 PM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>00</v>
+        <v>032</v>
       </c>
       <c r="B4" t="str">
-        <v>19/3/2025, 12:09:57 pm</v>
+        <v>4/22/2026, 12:12:09 PM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>00</v>
+        <v>031</v>
       </c>
       <c r="B5" t="str">
-        <v>19/3/2025, 12:10:57 pm</v>
+        <v>4/22/2026, 12:13:09 PM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>025</v>
+        <v>031</v>
       </c>
       <c r="B6" t="str">
-        <v>19/3/2025, 2:27:45 pm</v>
+        <v>4/22/2026, 12:13:09 PM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2560</v>
+        <v>030</v>
       </c>
       <c r="B7" t="str">
-        <v>19/3/2025, 2:28:45 pm</v>
+        <v>4/22/2026, 12:14:09 PM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0101</v>
+        <v>0135</v>
       </c>
       <c r="B8" t="str">
-        <v>19/3/2025, 2:29:45 pm</v>
+        <v>4/22/2026, 12:15:09 PM</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>01</v>
+        <v>0135</v>
       </c>
       <c r="B9" t="str">
-        <v>19/3/2025, 2:30:45 pm</v>
+        <v>4/22/2026, 12:15:09 PM</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>00</v>
+        <v>02</v>
       </c>
       <c r="B10" t="str">
-        <v>19/3/2025, 2:31:45 pm</v>
+        <v>4/22/2026, 12:16:09 PM</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>024</v>
+        <v>51294</v>
       </c>
       <c r="B11" t="str">
-        <v>19/3/2025, 2:40:45 pm</v>
+        <v>4/22/2026, 12:17:09 PM</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>024</v>
+        <v>51294</v>
       </c>
       <c r="B12" t="str">
-        <v>19/3/2025, 2:41:45 pm</v>
+        <v>4/22/2026, 12:17:09 PM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B186"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>51215</v>
+      </c>
+      <c r="B2" t="str">
+        <v>5/5/2026, 1:06:16 PM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>043</v>
+      </c>
+      <c r="B3" t="str">
+        <v>5/5/2026, 1:07:16 PM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>043</v>
+      </c>
+      <c r="B4" t="str">
+        <v>5/5/2026, 1:07:17 PM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>052</v>
+      </c>
+      <c r="B5" t="str">
+        <v>5/5/2026, 1:08:16 PM</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>036</v>
+      </c>
+      <c r="B6" t="str">
+        <v>5/5/2026, 1:09:16 PM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>040</v>
+      </c>
+      <c r="B7" t="str">
+        <v>5/5/2026, 1:10:16 PM</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>0106</v>
+      </c>
+      <c r="B8" t="str">
+        <v>5/5/2026, 1:11:16 PM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>01</v>
+      </c>
+      <c r="B9" t="str">
+        <v>5/5/2026, 1:12:16 PM</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>256198</v>
+      </c>
+      <c r="B10" t="str">
+        <v>5/5/2026, 1:13:16 PM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>256198</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5/5/2026, 1:13:17 PM</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>070</v>
+      </c>
+      <c r="B12" t="str">
+        <v>5/5/2026, 1:14:16 PM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>026</v>
+        <v>047</v>
       </c>
       <c r="B13" t="str">
-        <v>19/3/2025, 2:42:45 pm</v>
+        <v>5/5/2026, 1:15:17 PM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>00</v>
+        <v>061</v>
       </c>
       <c r="B14" t="str">
-        <v>19/3/2025, 2:43:47 pm</v>
+        <v>5/5/2026, 1:16:16 PM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>00</v>
+        <v>056</v>
       </c>
       <c r="B15" t="str">
-        <v>19/3/2025, 2:43:49 pm</v>
+        <v>5/5/2026, 1:17:16 PM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>099</v>
+        <v>0183</v>
       </c>
       <c r="B16" t="str">
-        <v>19/3/2025, 2:44:45 pm</v>
+        <v>5/5/2026, 1:18:16 PM</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>045</v>
+      </c>
+      <c r="B17" t="str">
+        <v>5/5/2026, 1:21:16 PM</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>045</v>
+      </c>
+      <c r="B18" t="str">
+        <v>5/5/2026, 1:21:17 PM</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>032</v>
+      </c>
+      <c r="B19" t="str">
+        <v>5/5/2026, 1:22:16 PM</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>033</v>
+      </c>
+      <c r="B20" t="str">
+        <v>5/5/2026, 1:23:16 PM</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>032</v>
+      </c>
+      <c r="B21" t="str">
+        <v>5/5/2026, 1:24:20 PM</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>036</v>
+      </c>
+      <c r="B22" t="str">
+        <v>5/5/2026, 1:28:16 PM</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>036</v>
+      </c>
+      <c r="B23" t="str">
+        <v>5/5/2026, 1:29:16 PM</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>034</v>
+      </c>
+      <c r="B24" t="str">
+        <v>5/5/2026, 1:30:17 PM</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>033</v>
+      </c>
+      <c r="B25" t="str">
+        <v>5/5/2026, 1:31:16 PM</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>091</v>
+      </c>
+      <c r="B26" t="str">
+        <v>5/5/2026, 1:32:16 PM</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>01</v>
+      </c>
+      <c r="B27" t="str">
+        <v>5/5/2026, 1:33:16 PM</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>00</v>
+      </c>
+      <c r="B28" t="str">
+        <v>5/5/2026, 1:34:16 PM</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>031</v>
+      </c>
+      <c r="B29" t="str">
+        <v>5/5/2026, 1:35:16 PM</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>033</v>
+      </c>
+      <c r="B30" t="str">
+        <v>5/5/2026, 1:36:16 PM</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>033</v>
+      </c>
+      <c r="B31" t="str">
+        <v>5/5/2026, 1:36:17 PM</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>033</v>
+      </c>
+      <c r="B32" t="str">
+        <v>5/5/2026, 1:36:17 PM</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>031</v>
+      </c>
+      <c r="B33" t="str">
+        <v>5/5/2026, 1:37:16 PM</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>034</v>
+      </c>
+      <c r="B34" t="str">
+        <v>5/5/2026, 1:38:16 PM</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>097</v>
+      </c>
+      <c r="B35" t="str">
+        <v>5/5/2026, 1:39:16 PM</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>01</v>
+      </c>
+      <c r="B36" t="str">
+        <v>5/5/2026, 1:40:16 PM</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>256215</v>
+      </c>
+      <c r="B37" t="str">
+        <v>5/5/2026, 1:41:16 PM</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>033</v>
+      </c>
+      <c r="B38" t="str">
+        <v>5/5/2026, 1:42:16 PM</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>035</v>
+      </c>
+      <c r="B39" t="str">
+        <v>5/5/2026, 1:43:16 PM</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>033</v>
+      </c>
+      <c r="B40" t="str">
+        <v>5/5/2026, 1:44:17 PM</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>031</v>
+      </c>
+      <c r="B41" t="str">
+        <v>5/5/2026, 1:45:16 PM</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>092</v>
+      </c>
+      <c r="B42" t="str">
+        <v>5/5/2026, 1:46:16 PM</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>01</v>
+      </c>
+      <c r="B43" t="str">
+        <v>5/5/2026, 1:47:16 PM</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>256195</v>
+      </c>
+      <c r="B44" t="str">
+        <v>5/5/2026, 1:48:16 PM</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>256195</v>
+      </c>
+      <c r="B45" t="str">
+        <v>5/5/2026, 1:48:17 PM</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>030</v>
+      </c>
+      <c r="B46" t="str">
+        <v>5/5/2026, 1:49:16 PM</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>032</v>
+      </c>
+      <c r="B47" t="str">
+        <v>5/5/2026, 1:50:16 PM</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>042</v>
+      </c>
+      <c r="B48" t="str">
+        <v>5/5/2026, 1:51:16 PM</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>034</v>
+      </c>
+      <c r="B49" t="str">
+        <v>5/5/2026, 1:52:16 PM</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>0168</v>
+      </c>
+      <c r="B50" t="str">
+        <v>5/5/2026, 1:53:17 PM</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>01</v>
+      </c>
+      <c r="B51" t="str">
+        <v>5/5/2026, 1:54:16 PM</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>01</v>
+      </c>
+      <c r="B52" t="str">
+        <v>5/5/2026, 1:54:17 PM</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>256222</v>
+      </c>
+      <c r="B53" t="str">
+        <v>5/5/2026, 1:55:16 PM</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>035</v>
+      </c>
+      <c r="B54" t="str">
+        <v>5/5/2026, 1:56:24 PM</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>037</v>
+      </c>
+      <c r="B55" t="str">
+        <v>5/5/2026, 1:57:16 PM</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>037</v>
+      </c>
+      <c r="B56" t="str">
+        <v>5/5/2026, 1:58:16 PM</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>035</v>
+      </c>
+      <c r="B57" t="str">
+        <v>5/5/2026, 1:59:17 PM</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>0187</v>
+      </c>
+      <c r="B58" t="str">
+        <v>5/5/2026, 2:00:16 PM</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>01</v>
+      </c>
+      <c r="B59" t="str">
+        <v>5/5/2026, 2:01:17 PM</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>256208</v>
+      </c>
+      <c r="B60" t="str">
+        <v>5/5/2026, 2:02:16 PM</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>033</v>
+      </c>
+      <c r="B61" t="str">
+        <v>5/5/2026, 2:03:16 PM</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>035</v>
+      </c>
+      <c r="B62" t="str">
+        <v>5/5/2026, 2:04:17 PM</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>037</v>
+      </c>
+      <c r="B63" t="str">
+        <v>5/5/2026, 2:05:16 PM</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>037</v>
+      </c>
+      <c r="B64" t="str">
+        <v>5/5/2026, 2:06:16 PM</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>0145</v>
+      </c>
+      <c r="B65" t="str">
+        <v>5/5/2026, 2:07:16 PM</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>01</v>
+      </c>
+      <c r="B66" t="str">
+        <v>5/5/2026, 2:08:17 PM</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>256194</v>
+      </c>
+      <c r="B67" t="str">
+        <v>5/5/2026, 2:09:26 PM</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>032</v>
+      </c>
+      <c r="B68" t="str">
+        <v>5/5/2026, 2:10:16 PM</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>036</v>
+      </c>
+      <c r="B69" t="str">
+        <v>5/5/2026, 2:11:16 PM</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>036</v>
+      </c>
+      <c r="B70" t="str">
+        <v>5/5/2026, 2:11:17 PM</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>051</v>
+      </c>
+      <c r="B71" t="str">
+        <v>5/5/2026, 2:12:17 PM</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>061</v>
+      </c>
+      <c r="B72" t="str">
+        <v>5/5/2026, 2:13:17 PM</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>0158</v>
+      </c>
+      <c r="B73" t="str">
+        <v>5/5/2026, 2:14:16 PM</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>01</v>
+      </c>
+      <c r="B74" t="str">
+        <v>5/5/2026, 2:15:17 PM</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>256219</v>
+      </c>
+      <c r="B75" t="str">
+        <v>5/5/2026, 2:16:16 PM</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>053</v>
+      </c>
+      <c r="B76" t="str">
+        <v>5/5/2026, 2:17:17 PM</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>051</v>
+      </c>
+      <c r="B77" t="str">
+        <v>5/5/2026, 2:18:17 PM</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>037</v>
+      </c>
+      <c r="B78" t="str">
+        <v>5/5/2026, 2:19:17 PM</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>041</v>
+      </c>
+      <c r="B79" t="str">
+        <v>5/5/2026, 2:20:17 PM</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>0174</v>
+      </c>
+      <c r="B80" t="str">
+        <v>5/5/2026, 2:21:17 PM</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>01</v>
+      </c>
+      <c r="B81" t="str">
+        <v>5/5/2026, 2:22:17 PM</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>256231</v>
+      </c>
+      <c r="B82" t="str">
+        <v>5/5/2026, 2:23:17 PM</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>032</v>
+      </c>
+      <c r="B83" t="str">
+        <v>5/5/2026, 2:24:17 PM</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>037</v>
+      </c>
+      <c r="B84" t="str">
+        <v>5/5/2026, 2:25:17 PM</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>037</v>
+      </c>
+      <c r="B85" t="str">
+        <v>5/5/2026, 2:25:17 PM</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>042</v>
+      </c>
+      <c r="B86" t="str">
+        <v>5/5/2026, 2:26:17 PM</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>042</v>
+      </c>
+      <c r="B87" t="str">
+        <v>5/5/2026, 2:26:17 PM</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>042</v>
+      </c>
+      <c r="B88" t="str">
+        <v>5/5/2026, 2:26:17 PM</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>053</v>
+      </c>
+      <c r="B89" t="str">
+        <v>5/5/2026, 2:27:17 PM</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>053</v>
+      </c>
+      <c r="B90" t="str">
+        <v>5/5/2026, 2:27:17 PM</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>256115</v>
+      </c>
+      <c r="B91" t="str">
+        <v>5/5/2026, 2:28:17 PM</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>01</v>
+      </c>
+      <c r="B92" t="str">
+        <v>5/5/2026, 2:29:17 PM</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>512124</v>
+      </c>
+      <c r="B93" t="str">
+        <v>5/5/2026, 2:30:17 PM</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>050</v>
+      </c>
+      <c r="B94" t="str">
+        <v>5/5/2026, 2:31:17 PM</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>051</v>
+      </c>
+      <c r="B95" t="str">
+        <v>5/5/2026, 2:32:17 PM</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>045</v>
+      </c>
+      <c r="B96" t="str">
+        <v>5/5/2026, 2:33:17 PM</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>052</v>
+      </c>
+      <c r="B97" t="str">
+        <v>5/5/2026, 2:34:17 PM</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>256113</v>
+      </c>
+      <c r="B98" t="str">
+        <v>5/5/2026, 2:35:17 PM</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>01</v>
+      </c>
+      <c r="B99" t="str">
+        <v>5/5/2026, 2:36:17 PM</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>51278</v>
+      </c>
+      <c r="B100" t="str">
+        <v>5/5/2026, 2:37:17 PM</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>040</v>
+      </c>
+      <c r="B101" t="str">
+        <v>5/5/2026, 2:38:17 PM</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>047</v>
+      </c>
+      <c r="B102" t="str">
+        <v>5/5/2026, 2:39:17 PM</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>047</v>
+      </c>
+      <c r="B103" t="str">
+        <v>5/5/2026, 2:39:17 PM</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>052</v>
+      </c>
+      <c r="B104" t="str">
+        <v>5/5/2026, 2:40:17 PM</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>047</v>
+      </c>
+      <c r="B105" t="str">
+        <v>5/5/2026, 2:41:17 PM</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>25611</v>
+      </c>
+      <c r="B106" t="str">
+        <v>5/5/2026, 2:42:17 PM</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>25611</v>
+      </c>
+      <c r="B107" t="str">
+        <v>5/5/2026, 2:42:17 PM</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>256198</v>
+      </c>
+      <c r="B108" t="str">
+        <v>5/5/2026, 4:01:17 PM</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>033</v>
+      </c>
+      <c r="B109" t="str">
+        <v>5/5/2026, 4:02:17 PM</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>031</v>
+      </c>
+      <c r="B110" t="str">
+        <v>5/5/2026, 4:03:17 PM</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>031</v>
+      </c>
+      <c r="B111" t="str">
+        <v>5/5/2026, 4:04:17 PM</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>029</v>
+      </c>
+      <c r="B112" t="str">
+        <v>5/5/2026, 4:05:17 PM</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>0109</v>
+      </c>
+      <c r="B113" t="str">
+        <v>5/5/2026, 4:06:17 PM</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>01</v>
+      </c>
+      <c r="B114" t="str">
+        <v>5/5/2026, 4:07:17 PM</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>256200</v>
+      </c>
+      <c r="B115" t="str">
+        <v>5/5/2026, 4:08:17 PM</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>029</v>
+      </c>
+      <c r="B116" t="str">
+        <v>5/5/2026, 4:09:17 PM</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>029</v>
+      </c>
+      <c r="B117" t="str">
+        <v>5/5/2026, 4:10:17 PM</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>031</v>
+      </c>
+      <c r="B118" t="str">
+        <v>5/5/2026, 4:11:17 PM</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>030</v>
+      </c>
+      <c r="B119" t="str">
+        <v>5/5/2026, 4:12:17 PM</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>0106</v>
+      </c>
+      <c r="B120" t="str">
+        <v>5/5/2026, 4:13:17 PM</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>01</v>
+      </c>
+      <c r="B121" t="str">
+        <v>5/5/2026, 4:14:17 PM</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>256200</v>
+      </c>
+      <c r="B122" t="str">
+        <v>5/5/2026, 4:15:17 PM</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>030</v>
+      </c>
+      <c r="B123" t="str">
+        <v>5/5/2026, 4:16:17 PM</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>032</v>
+      </c>
+      <c r="B124" t="str">
+        <v>5/5/2026, 4:17:17 PM</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>031</v>
+      </c>
+      <c r="B125" t="str">
+        <v>5/5/2026, 4:18:17 PM</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>031</v>
+      </c>
+      <c r="B126" t="str">
+        <v>5/5/2026, 4:19:17 PM</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>0131</v>
+      </c>
+      <c r="B127" t="str">
+        <v>5/5/2026, 4:20:17 PM</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>01</v>
+      </c>
+      <c r="B128" t="str">
+        <v>5/5/2026, 4:21:17 PM</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>00</v>
+      </c>
+      <c r="B129" t="str">
+        <v>5/5/2026, 4:22:17 PM</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>030</v>
+      </c>
+      <c r="B130" t="str">
+        <v>5/5/2026, 4:23:17 PM</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>030</v>
+      </c>
+      <c r="B131" t="str">
+        <v>5/5/2026, 4:24:17 PM</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>031</v>
+      </c>
+      <c r="B132" t="str">
+        <v>5/5/2026, 4:25:17 PM</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>032</v>
+      </c>
+      <c r="B133" t="str">
+        <v>5/5/2026, 4:26:17 PM</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>0120</v>
+      </c>
+      <c r="B134" t="str">
+        <v>5/5/2026, 4:27:17 PM</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>01</v>
+      </c>
+      <c r="B135" t="str">
+        <v>5/5/2026, 4:28:17 PM</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>00</v>
+      </c>
+      <c r="B136" t="str">
+        <v>5/5/2026, 4:29:17 PM</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>029</v>
+      </c>
+      <c r="B137" t="str">
+        <v>5/5/2026, 4:30:17 PM</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>027</v>
+      </c>
+      <c r="B138" t="str">
+        <v>5/5/2026, 4:31:17 PM</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>029</v>
+      </c>
+      <c r="B139" t="str">
+        <v>5/5/2026, 4:32:17 PM</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>030</v>
+      </c>
+      <c r="B140" t="str">
+        <v>5/5/2026, 4:33:17 PM</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>0152</v>
+      </c>
+      <c r="B141" t="str">
+        <v>5/5/2026, 4:34:17 PM</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>01</v>
+      </c>
+      <c r="B142" t="str">
+        <v>5/5/2026, 4:35:17 PM</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>256228</v>
+      </c>
+      <c r="B143" t="str">
+        <v>5/5/2026, 4:36:17 PM</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>027</v>
+      </c>
+      <c r="B144" t="str">
+        <v>5/5/2026, 4:37:17 PM</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>030</v>
+      </c>
+      <c r="B145" t="str">
+        <v>5/5/2026, 4:38:17 PM</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>030</v>
+      </c>
+      <c r="B146" t="str">
+        <v>5/5/2026, 4:39:17 PM</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>028</v>
+      </c>
+      <c r="B147" t="str">
+        <v>5/5/2026, 4:40:17 PM</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>0167</v>
+      </c>
+      <c r="B148" t="str">
+        <v>5/5/2026, 4:41:17 PM</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>0167</v>
+      </c>
+      <c r="B149" t="str">
+        <v>5/5/2026, 4:41:17 PM</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>01</v>
+      </c>
+      <c r="B150" t="str">
+        <v>5/5/2026, 4:42:17 PM</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>01</v>
+      </c>
+      <c r="B151" t="str">
+        <v>5/5/2026, 4:42:17 PM</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>00</v>
+      </c>
+      <c r="B152" t="str">
+        <v>5/5/2026, 4:43:17 PM</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>029</v>
+      </c>
+      <c r="B153" t="str">
+        <v>5/5/2026, 4:44:17 PM</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>028</v>
+      </c>
+      <c r="B154" t="str">
+        <v>5/5/2026, 4:45:17 PM</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>030</v>
+      </c>
+      <c r="B155" t="str">
+        <v>5/5/2026, 4:46:17 PM</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>031</v>
+      </c>
+      <c r="B156" t="str">
+        <v>5/5/2026, 4:47:17 PM</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>0170</v>
+      </c>
+      <c r="B157" t="str">
+        <v>5/5/2026, 4:48:17 PM</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>01</v>
+      </c>
+      <c r="B158" t="str">
+        <v>5/5/2026, 4:49:17 PM</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>00</v>
+      </c>
+      <c r="B159" t="str">
+        <v>5/5/2026, 4:50:17 PM</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>029</v>
+      </c>
+      <c r="B160" t="str">
+        <v>5/5/2026, 4:51:17 PM</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>029</v>
+      </c>
+      <c r="B161" t="str">
+        <v>5/5/2026, 4:52:17 PM</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>028</v>
+      </c>
+      <c r="B162" t="str">
+        <v>5/5/2026, 4:53:17 PM</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>028</v>
+      </c>
+      <c r="B163" t="str">
+        <v>5/5/2026, 4:55:00 PM</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>027</v>
+      </c>
+      <c r="B164" t="str">
+        <v>5/5/2026, 4:55:59 PM</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>029</v>
+      </c>
+      <c r="B165" t="str">
+        <v>5/5/2026, 4:57:12 PM</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>027</v>
+      </c>
+      <c r="B166" t="str">
+        <v>5/5/2026, 4:57:59 PM</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>094</v>
+      </c>
+      <c r="B167" t="str">
+        <v>5/5/2026, 4:58:59 PM</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>01</v>
+      </c>
+      <c r="B168" t="str">
+        <v>5/5/2026, 5:00:00 PM</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>256208</v>
+      </c>
+      <c r="B169" t="str">
+        <v>5/5/2026, 5:00:59 PM</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>028</v>
+      </c>
+      <c r="B170" t="str">
+        <v>5/5/2026, 5:01:59 PM</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>028</v>
+      </c>
+      <c r="B171" t="str">
+        <v>5/5/2026, 5:03:01 PM</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>028</v>
+      </c>
+      <c r="B172" t="str">
+        <v>5/5/2026, 5:04:00 PM</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>028</v>
+      </c>
+      <c r="B173" t="str">
+        <v>5/5/2026, 5:06:07 PM</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>028</v>
+      </c>
+      <c r="B174" t="str">
+        <v>5/5/2026, 5:07:07 PM</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>027</v>
+      </c>
+      <c r="B175" t="str">
+        <v>5/5/2026, 5:08:07 PM</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>027</v>
+      </c>
+      <c r="B176" t="str">
+        <v>5/5/2026, 5:08:07 PM</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>028</v>
+      </c>
+      <c r="B177" t="str">
+        <v>5/5/2026, 5:09:07 PM</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>098</v>
+      </c>
+      <c r="B178" t="str">
+        <v>5/5/2026, 5:10:07 PM</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>01</v>
+      </c>
+      <c r="B179" t="str">
+        <v>5/5/2026, 5:11:07 PM</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>00</v>
+      </c>
+      <c r="B180" t="str">
+        <v>5/5/2026, 5:12:07 PM</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>025</v>
+      </c>
+      <c r="B181" t="str">
+        <v>5/5/2026, 5:13:07 PM</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>028</v>
+      </c>
+      <c r="B182" t="str">
+        <v>5/5/2026, 5:14:07 PM</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>028</v>
+      </c>
+      <c r="B183" t="str">
+        <v>5/5/2026, 5:15:07 PM</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>029</v>
+      </c>
+      <c r="B184" t="str">
+        <v>5/5/2026, 5:16:07 PM</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>0101</v>
+      </c>
+      <c r="B185" t="str">
+        <v>5/5/2026, 5:17:07 PM</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>01</v>
+      </c>
+      <c r="B186" t="str">
+        <v>5/5/2026, 5:18:08 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B186"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B145"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>031</v>
+      </c>
+      <c r="B2" t="str">
+        <v>5/6/2026, 3:27:39 PM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>028</v>
+      </c>
+      <c r="B3" t="str">
+        <v>5/6/2026, 3:28:39 PM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>029</v>
+      </c>
+      <c r="B4" t="str">
+        <v>5/6/2026, 3:29:39 PM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>0121</v>
+      </c>
+      <c r="B5" t="str">
+        <v>5/6/2026, 3:30:39 PM</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>01</v>
+      </c>
+      <c r="B6" t="str">
+        <v>5/6/2026, 3:31:39 PM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>256183</v>
+      </c>
+      <c r="B7" t="str">
+        <v>5/6/2026, 3:32:39 PM</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>029</v>
+      </c>
+      <c r="B8" t="str">
+        <v>5/6/2026, 3:33:39 PM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>028</v>
+      </c>
+      <c r="B9" t="str">
+        <v>5/6/2026, 3:34:39 PM</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>095</v>
+      </c>
+      <c r="B10" t="str">
+        <v>5/6/2026, 3:37:39 PM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>01</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5/6/2026, 3:38:39 PM</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>256189</v>
+      </c>
+      <c r="B12" t="str">
+        <v>5/6/2026, 3:39:39 PM</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>031</v>
+      </c>
+      <c r="B13" t="str">
+        <v>5/6/2026, 3:41:39 PM</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>029</v>
+      </c>
+      <c r="B14" t="str">
+        <v>5/6/2026, 3:42:39 PM</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>030</v>
+      </c>
+      <c r="B15" t="str">
+        <v>5/6/2026, 3:43:39 PM</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>0168</v>
+      </c>
+      <c r="B16" t="str">
+        <v>5/6/2026, 3:44:39 PM</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>01</v>
+      </c>
+      <c r="B17" t="str">
+        <v>5/6/2026, 3:45:39 PM</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>256201</v>
+      </c>
+      <c r="B18" t="str">
+        <v>5/6/2026, 3:46:39 PM</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>029</v>
+      </c>
+      <c r="B19" t="str">
+        <v>5/6/2026, 3:47:39 PM</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>027</v>
+      </c>
+      <c r="B20" t="str">
+        <v>5/6/2026, 3:48:40 PM</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>028</v>
+      </c>
+      <c r="B21" t="str">
+        <v>5/6/2026, 3:49:39 PM</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>027</v>
+      </c>
+      <c r="B22" t="str">
+        <v>5/6/2026, 3:50:39 PM</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>0123</v>
+      </c>
+      <c r="B23" t="str">
+        <v>5/6/2026, 3:51:39 PM</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>027</v>
+      </c>
+      <c r="B24" t="str">
+        <v>5/6/2026, 4:09:39 PM</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>028</v>
+      </c>
+      <c r="B25" t="str">
+        <v>5/6/2026, 4:10:39 PM</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>028</v>
+      </c>
+      <c r="B26" t="str">
+        <v>5/6/2026, 4:11:39 PM</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>063</v>
+      </c>
+      <c r="B27" t="str">
+        <v>5/6/2026, 4:12:39 PM</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>5/6/2026, 4:17:39 PM</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>027</v>
+      </c>
+      <c r="B29" t="str">
+        <v>5/6/2026, 4:18:39 PM</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>075</v>
+      </c>
+      <c r="B30" t="str">
+        <v>5/6/2026, 4:19:39 PM</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>01</v>
+      </c>
+      <c r="B31" t="str">
+        <v>5/6/2026, 4:20:39 PM</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>256177</v>
+      </c>
+      <c r="B32" t="str">
+        <v>5/6/2026, 4:21:39 PM</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>025</v>
+      </c>
+      <c r="B33" t="str">
+        <v>5/6/2026, 4:22:39 PM</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>027</v>
+      </c>
+      <c r="B34" t="str">
+        <v>5/6/2026, 4:23:39 PM</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>028</v>
+      </c>
+      <c r="B35" t="str">
+        <v>5/6/2026, 4:24:39 PM</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>026</v>
+      </c>
+      <c r="B36" t="str">
+        <v>5/6/2026, 4:25:39 PM</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>068</v>
+      </c>
+      <c r="B37" t="str">
+        <v>5/6/2026, 4:26:39 PM</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>01</v>
+      </c>
+      <c r="B38" t="str">
+        <v>5/6/2026, 4:27:39 PM</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>256167</v>
+      </c>
+      <c r="B39" t="str">
+        <v>5/6/2026, 4:28:39 PM</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>026</v>
+      </c>
+      <c r="B40" t="str">
+        <v>5/6/2026, 4:29:39 PM</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>025</v>
+      </c>
+      <c r="B41" t="str">
+        <v>5/6/2026, 4:30:39 PM</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>028</v>
+      </c>
+      <c r="B42" t="str">
+        <v>5/6/2026, 4:31:39 PM</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>024</v>
+      </c>
+      <c r="B43" t="str">
+        <v>5/6/2026, 4:32:39 PM</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>075</v>
+      </c>
+      <c r="B44" t="str">
+        <v>5/6/2026, 4:33:40 PM</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>01</v>
+      </c>
+      <c r="B45" t="str">
+        <v>5/6/2026, 4:34:39 PM</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>256169</v>
+      </c>
+      <c r="B46" t="str">
+        <v>5/6/2026, 4:35:39 PM</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>024</v>
+      </c>
+      <c r="B47" t="str">
+        <v>5/6/2026, 4:36:40 PM</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>027</v>
+      </c>
+      <c r="B48" t="str">
+        <v>5/6/2026, 4:37:39 PM</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>025</v>
+      </c>
+      <c r="B49" t="str">
+        <v>5/6/2026, 4:38:39 PM</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>026</v>
+      </c>
+      <c r="B50" t="str">
+        <v>5/6/2026, 4:39:39 PM</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>061</v>
+      </c>
+      <c r="B51" t="str">
+        <v>5/6/2026, 4:40:39 PM</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>01</v>
+      </c>
+      <c r="B52" t="str">
+        <v>5/6/2026, 4:41:39 PM</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>256179</v>
+      </c>
+      <c r="B53" t="str">
+        <v>5/6/2026, 4:42:39 PM</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>024</v>
+      </c>
+      <c r="B54" t="str">
+        <v>5/6/2026, 4:43:39 PM</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>027</v>
+      </c>
+      <c r="B55" t="str">
+        <v>5/6/2026, 4:44:39 PM</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>025</v>
+      </c>
+      <c r="B56" t="str">
+        <v>5/6/2026, 4:45:39 PM</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>025</v>
+      </c>
+      <c r="B57" t="str">
+        <v>5/6/2026, 4:45:39 PM</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>025</v>
+      </c>
+      <c r="B58" t="str">
+        <v>5/6/2026, 4:46:39 PM</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>065</v>
+      </c>
+      <c r="B59" t="str">
+        <v>5/6/2026, 4:47:40 PM</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>01</v>
+      </c>
+      <c r="B60" t="str">
+        <v>5/6/2026, 4:48:39 PM</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>256184</v>
+      </c>
+      <c r="B61" t="str">
+        <v>5/6/2026, 4:49:39 PM</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>026</v>
+      </c>
+      <c r="B62" t="str">
+        <v>5/6/2026, 4:50:39 PM</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>026</v>
+      </c>
+      <c r="B63" t="str">
+        <v>5/6/2026, 4:51:39 PM</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>026</v>
+      </c>
+      <c r="B64" t="str">
+        <v>5/6/2026, 4:52:39 PM</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>026</v>
+      </c>
+      <c r="B65" t="str">
+        <v>5/6/2026, 4:53:39 PM</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>066</v>
+      </c>
+      <c r="B66" t="str">
+        <v>5/6/2026, 4:54:39 PM</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>01</v>
+      </c>
+      <c r="B67" t="str">
+        <v>5/6/2026, 4:55:39 PM</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>256175</v>
+      </c>
+      <c r="B68" t="str">
+        <v>5/6/2026, 4:56:39 PM</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>025</v>
+      </c>
+      <c r="B69" t="str">
+        <v>5/6/2026, 4:57:39 PM</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>026</v>
+      </c>
+      <c r="B70" t="str">
+        <v>5/6/2026, 4:58:39 PM</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>024</v>
+      </c>
+      <c r="B71" t="str">
+        <v>5/6/2026, 4:59:39 PM</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>026</v>
+      </c>
+      <c r="B72" t="str">
+        <v>5/6/2026, 5:00:39 PM</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>053</v>
+      </c>
+      <c r="B73" t="str">
+        <v>5/6/2026, 5:01:39 PM</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>01</v>
+      </c>
+      <c r="B74" t="str">
+        <v>5/6/2026, 5:02:39 PM</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>256179</v>
+      </c>
+      <c r="B75" t="str">
+        <v>5/6/2026, 5:03:39 PM</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>025</v>
+      </c>
+      <c r="B76" t="str">
+        <v>5/6/2026, 5:04:39 PM</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>027</v>
+      </c>
+      <c r="B77" t="str">
+        <v>5/6/2026, 5:05:39 PM</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>057</v>
+      </c>
+      <c r="B78" t="str">
+        <v>5/6/2026, 5:08:39 PM</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>01</v>
+      </c>
+      <c r="B79" t="str">
+        <v>5/6/2026, 5:09:39 PM</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>256221</v>
+      </c>
+      <c r="B80" t="str">
+        <v>5/6/2026, 5:10:39 PM</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>025</v>
+      </c>
+      <c r="B81" t="str">
+        <v>5/6/2026, 5:11:39 PM</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>028</v>
+      </c>
+      <c r="B82" t="str">
+        <v>5/6/2026, 5:12:39 PM</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>025</v>
+      </c>
+      <c r="B83" t="str">
+        <v>5/6/2026, 5:13:39 PM</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>029</v>
+      </c>
+      <c r="B84" t="str">
+        <v>5/6/2026, 5:14:39 PM</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>0108</v>
+      </c>
+      <c r="B85" t="str">
+        <v>5/6/2026, 5:15:39 PM</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>01</v>
+      </c>
+      <c r="B86" t="str">
+        <v>5/6/2026, 5:16:39 PM</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>5121</v>
+      </c>
+      <c r="B87" t="str">
+        <v>5/6/2026, 5:17:39 PM</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>027</v>
+      </c>
+      <c r="B88" t="str">
+        <v>5/6/2026, 5:18:39 PM</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>029</v>
+      </c>
+      <c r="B89" t="str">
+        <v>5/6/2026, 5:19:39 PM</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>028</v>
+      </c>
+      <c r="B90" t="str">
+        <v>5/6/2026, 5:20:39 PM</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>026</v>
+      </c>
+      <c r="B91" t="str">
+        <v>5/6/2026, 5:21:39 PM</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>074</v>
+      </c>
+      <c r="B92" t="str">
+        <v>5/6/2026, 5:22:39 PM</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>01</v>
+      </c>
+      <c r="B93" t="str">
+        <v>5/6/2026, 5:23:39 PM</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>256242</v>
+      </c>
+      <c r="B94" t="str">
+        <v>5/6/2026, 5:24:39 PM</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>028</v>
+      </c>
+      <c r="B95" t="str">
+        <v>5/6/2026, 5:25:39 PM</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>027</v>
+      </c>
+      <c r="B96" t="str">
+        <v>5/6/2026, 5:26:43 PM</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>026</v>
+      </c>
+      <c r="B97" t="str">
+        <v>5/6/2026, 5:27:39 PM</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>026</v>
+      </c>
+      <c r="B98" t="str">
+        <v>5/6/2026, 5:28:39 PM</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>083</v>
+      </c>
+      <c r="B99" t="str">
+        <v>5/6/2026, 5:29:39 PM</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>01</v>
+      </c>
+      <c r="B100" t="str">
+        <v>5/6/2026, 5:30:39 PM</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>256224</v>
+      </c>
+      <c r="B101" t="str">
+        <v>5/6/2026, 5:31:39 PM</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>028</v>
+      </c>
+      <c r="B102" t="str">
+        <v>5/6/2026, 5:32:39 PM</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>029</v>
+      </c>
+      <c r="B103" t="str">
+        <v>5/6/2026, 5:33:39 PM</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>030</v>
+      </c>
+      <c r="B104" t="str">
+        <v>5/6/2026, 5:34:39 PM</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>027</v>
+      </c>
+      <c r="B105" t="str">
+        <v>5/6/2026, 5:35:39 PM</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>064</v>
+      </c>
+      <c r="B106" t="str">
+        <v>5/6/2026, 5:36:39 PM</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>01</v>
+      </c>
+      <c r="B107" t="str">
+        <v>5/6/2026, 5:37:39 PM</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>256218</v>
+      </c>
+      <c r="B108" t="str">
+        <v>5/6/2026, 5:38:39 PM</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>028</v>
+      </c>
+      <c r="B109" t="str">
+        <v>5/6/2026, 5:39:39 PM</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>029</v>
+      </c>
+      <c r="B110" t="str">
+        <v>5/6/2026, 5:40:39 PM</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>030</v>
+      </c>
+      <c r="B111" t="str">
+        <v>5/6/2026, 5:41:39 PM</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>027</v>
+      </c>
+      <c r="B112" t="str">
+        <v>5/6/2026, 5:42:39 PM</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>045</v>
+      </c>
+      <c r="B113" t="str">
+        <v>5/6/2026, 5:43:39 PM</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>01</v>
+      </c>
+      <c r="B114" t="str">
+        <v>5/6/2026, 5:44:39 PM</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>256201</v>
+      </c>
+      <c r="B115" t="str">
+        <v>5/6/2026, 5:45:39 PM</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>031</v>
+      </c>
+      <c r="B116" t="str">
+        <v>5/6/2026, 5:46:39 PM</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>030</v>
+      </c>
+      <c r="B117" t="str">
+        <v>5/6/2026, 5:47:39 PM</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>031</v>
+      </c>
+      <c r="B118" t="str">
+        <v>5/6/2026, 5:48:39 PM</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>030</v>
+      </c>
+      <c r="B119" t="str">
+        <v>5/6/2026, 5:49:39 PM</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>050</v>
+      </c>
+      <c r="B120" t="str">
+        <v>5/6/2026, 5:50:39 PM</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>01</v>
+      </c>
+      <c r="B121" t="str">
+        <v>5/6/2026, 5:51:39 PM</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>256190</v>
+      </c>
+      <c r="B122" t="str">
+        <v>5/6/2026, 5:52:39 PM</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>030</v>
+      </c>
+      <c r="B123" t="str">
+        <v>5/6/2026, 5:53:39 PM</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>031</v>
+      </c>
+      <c r="B124" t="str">
+        <v>5/6/2026, 5:54:39 PM</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>030</v>
+      </c>
+      <c r="B125" t="str">
+        <v>5/6/2026, 5:55:39 PM</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>029</v>
+      </c>
+      <c r="B126" t="str">
+        <v>5/6/2026, 5:56:39 PM</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>053</v>
+      </c>
+      <c r="B127" t="str">
+        <v>5/6/2026, 5:57:39 PM</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>01</v>
+      </c>
+      <c r="B128" t="str">
+        <v>5/6/2026, 5:58:40 PM</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>256209</v>
+      </c>
+      <c r="B129" t="str">
+        <v>5/6/2026, 5:59:39 PM</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>030</v>
+      </c>
+      <c r="B130" t="str">
+        <v>5/6/2026, 6:00:39 PM</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>030</v>
+      </c>
+      <c r="B131" t="str">
+        <v>5/6/2026, 6:01:39 PM</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>030</v>
+      </c>
+      <c r="B132" t="str">
+        <v>5/6/2026, 6:02:39 PM</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>032</v>
+      </c>
+      <c r="B133" t="str">
+        <v>5/6/2026, 6:03:39 PM</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>0123</v>
+      </c>
+      <c r="B134" t="str">
+        <v>5/6/2026, 6:04:39 PM</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>02</v>
+      </c>
+      <c r="B135" t="str">
+        <v>5/6/2026, 6:05:39 PM</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>51239</v>
+      </c>
+      <c r="B136" t="str">
+        <v>5/6/2026, 6:06:39 PM</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>031</v>
+      </c>
+      <c r="B137" t="str">
+        <v>5/6/2026, 6:07:39 PM</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>032</v>
+      </c>
+      <c r="B138" t="str">
+        <v>5/6/2026, 6:08:39 PM</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>031</v>
+      </c>
+      <c r="B139" t="str">
+        <v>5/6/2026, 6:09:39 PM</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>029</v>
+      </c>
+      <c r="B140" t="str">
+        <v>5/6/2026, 6:10:40 PM</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>077</v>
+      </c>
+      <c r="B141" t="str">
+        <v>5/6/2026, 6:11:39 PM</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>02</v>
+      </c>
+      <c r="B142" t="str">
+        <v>5/6/2026, 6:12:39 PM</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>02</v>
+      </c>
+      <c r="B143" t="str">
+        <v>5/6/2026, 6:12:40 PM</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>256237</v>
+      </c>
+      <c r="B144" t="str">
+        <v>5/6/2026, 6:13:39 PM</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>031</v>
+      </c>
+      <c r="B145" t="str">
+        <v>5/6/2026, 6:14:39 PM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B145"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>020</v>
+      </c>
+      <c r="B2" t="str">
+        <v>5/13/2026, 4:30:48 PM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>045</v>
+      </c>
+      <c r="B3" t="str">
+        <v>5/13/2026, 4:57:00 PM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>016</v>
+      </c>
+      <c r="B4" t="str">
+        <v>5/13/2026, 4:57:46 PM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>016</v>
+      </c>
+      <c r="B5" t="str">
+        <v>5/13/2026, 4:58:46 PM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B213"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>0244</v>
+      </c>
+      <c r="B2" t="str">
+        <v>5/16/2026, 12:41:47 PM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>01</v>
+      </c>
+      <c r="B3" t="str">
+        <v>5/16/2026, 12:42:47 PM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>043</v>
+      </c>
+      <c r="B4" t="str">
+        <v>5/16/2026, 12:44:47 PM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>045</v>
+      </c>
+      <c r="B5" t="str">
+        <v>5/16/2026, 12:45:47 PM</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>047</v>
+      </c>
+      <c r="B6" t="str">
+        <v>5/16/2026, 12:46:47 PM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>044</v>
+      </c>
+      <c r="B7" t="str">
+        <v>5/16/2026, 12:47:47 PM</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>256175</v>
+      </c>
+      <c r="B8" t="str">
+        <v>5/16/2026, 12:48:47 PM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>01</v>
+      </c>
+      <c r="B9" t="str">
+        <v>5/16/2026, 12:49:47 PM</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1280163</v>
+      </c>
+      <c r="B10" t="str">
+        <v>5/16/2026, 12:50:47 PM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>044</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5/16/2026, 12:51:47 PM</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>044</v>
+      </c>
+      <c r="B12" t="str">
+        <v>5/16/2026, 12:52:47 PM</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>042</v>
+      </c>
+      <c r="B13" t="str">
+        <v>5/16/2026, 12:53:47 PM</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>044</v>
+      </c>
+      <c r="B14" t="str">
+        <v>5/16/2026, 12:54:47 PM</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>256172</v>
+      </c>
+      <c r="B15" t="str">
+        <v>5/16/2026, 12:55:47 PM</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>01</v>
+      </c>
+      <c r="B16" t="str">
+        <v>5/16/2026, 12:56:47 PM</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1280251</v>
+      </c>
+      <c r="B17" t="str">
+        <v>5/16/2026, 12:57:47 PM</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>039</v>
+      </c>
+      <c r="B18" t="str">
+        <v>5/16/2026, 12:58:47 PM</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>043</v>
+      </c>
+      <c r="B19" t="str">
+        <v>5/16/2026, 12:59:47 PM</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>040</v>
+      </c>
+      <c r="B20" t="str">
+        <v>5/16/2026, 1:00:47 PM</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>041</v>
+      </c>
+      <c r="B21" t="str">
+        <v>5/16/2026, 1:01:47 PM</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>256158</v>
+      </c>
+      <c r="B22" t="str">
+        <v>5/16/2026, 1:02:47 PM</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>01</v>
+      </c>
+      <c r="B23" t="str">
+        <v>5/16/2026, 1:03:47 PM</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>153636</v>
+      </c>
+      <c r="B24" t="str">
+        <v>5/16/2026, 1:04:47 PM</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>038</v>
+      </c>
+      <c r="B25" t="str">
+        <v>5/16/2026, 1:05:47 PM</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>039</v>
+      </c>
+      <c r="B26" t="str">
+        <v>5/16/2026, 1:06:47 PM</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>036</v>
+      </c>
+      <c r="B27" t="str">
+        <v>5/16/2026, 1:07:47 PM</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>039</v>
+      </c>
+      <c r="B28" t="str">
+        <v>5/16/2026, 1:08:47 PM</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>256107</v>
+      </c>
+      <c r="B29" t="str">
+        <v>5/16/2026, 1:09:47 PM</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>01</v>
+      </c>
+      <c r="B30" t="str">
+        <v>5/16/2026, 1:10:47 PM</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>1536200</v>
+      </c>
+      <c r="B31" t="str">
+        <v>5/16/2026, 1:11:47 PM</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>036</v>
+      </c>
+      <c r="B32" t="str">
+        <v>5/16/2026, 1:26:29 PM</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>036</v>
+      </c>
+      <c r="B33" t="str">
+        <v>5/16/2026, 1:27:47 PM</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>034</v>
+      </c>
+      <c r="B34" t="str">
+        <v>5/16/2026, 1:28:47 PM</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>035</v>
+      </c>
+      <c r="B35" t="str">
+        <v>5/16/2026, 1:29:47 PM</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>25644</v>
+      </c>
+      <c r="B36" t="str">
+        <v>5/16/2026, 1:30:47 PM</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>01</v>
+      </c>
+      <c r="B37" t="str">
+        <v>5/16/2026, 1:31:47 PM</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>179283</v>
+      </c>
+      <c r="B38" t="str">
+        <v>5/16/2026, 1:32:47 PM</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>034</v>
+      </c>
+      <c r="B39" t="str">
+        <v>5/16/2026, 1:33:47 PM</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>037</v>
+      </c>
+      <c r="B40" t="str">
+        <v>5/16/2026, 1:34:47 PM</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>036</v>
+      </c>
+      <c r="B41" t="str">
+        <v>5/16/2026, 1:35:47 PM</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>035</v>
+      </c>
+      <c r="B42" t="str">
+        <v>5/16/2026, 1:36:47 PM</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>25615</v>
+      </c>
+      <c r="B43" t="str">
+        <v>5/16/2026, 1:37:47 PM</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>25615</v>
+      </c>
+      <c r="B44" t="str">
+        <v>5/16/2026, 1:37:47 PM</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>01</v>
+      </c>
+      <c r="B45" t="str">
+        <v>5/16/2026, 1:38:47 PM</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>17928</v>
+      </c>
+      <c r="B46" t="str">
+        <v>5/16/2026, 1:39:47 PM</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>036</v>
+      </c>
+      <c r="B47" t="str">
+        <v>5/16/2026, 1:40:47 PM</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>035</v>
+      </c>
+      <c r="B48" t="str">
+        <v>5/16/2026, 1:42:19 PM</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>036</v>
+      </c>
+      <c r="B49" t="str">
+        <v>5/16/2026, 1:42:47 PM</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>037</v>
+      </c>
+      <c r="B50" t="str">
+        <v>5/16/2026, 1:43:47 PM</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>0246</v>
+      </c>
+      <c r="B51" t="str">
+        <v>5/16/2026, 1:44:47 PM</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>01</v>
+      </c>
+      <c r="B52" t="str">
+        <v>5/16/2026, 1:45:47 PM</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>1536186</v>
+      </c>
+      <c r="B53" t="str">
+        <v>5/16/2026, 1:46:47 PM</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>036</v>
+      </c>
+      <c r="B54" t="str">
+        <v>5/16/2026, 1:47:47 PM</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>038</v>
+      </c>
+      <c r="B55" t="str">
+        <v>5/16/2026, 1:48:47 PM</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>038</v>
+      </c>
+      <c r="B56" t="str">
+        <v>5/16/2026, 1:49:47 PM</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>037</v>
+      </c>
+      <c r="B57" t="str">
+        <v>5/16/2026, 1:50:47 PM</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>0225</v>
+      </c>
+      <c r="B58" t="str">
+        <v>5/16/2026, 1:51:47 PM</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>01</v>
+      </c>
+      <c r="B59" t="str">
+        <v>5/16/2026, 1:52:47 PM</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>1536164</v>
+      </c>
+      <c r="B60" t="str">
+        <v>5/16/2026, 1:53:47 PM</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>036</v>
+      </c>
+      <c r="B61" t="str">
+        <v>5/16/2026, 1:54:47 PM</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>038</v>
+      </c>
+      <c r="B62" t="str">
+        <v>5/16/2026, 1:55:47 PM</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>037</v>
+      </c>
+      <c r="B63" t="str">
+        <v>5/16/2026, 1:56:47 PM</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>036</v>
+      </c>
+      <c r="B64" t="str">
+        <v>5/16/2026, 1:57:47 PM</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>0207</v>
+      </c>
+      <c r="B65" t="str">
+        <v>5/16/2026, 1:58:47 PM</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>01</v>
+      </c>
+      <c r="B66" t="str">
+        <v>5/16/2026, 1:59:47 PM</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>1536113</v>
+      </c>
+      <c r="B67" t="str">
+        <v>5/16/2026, 2:00:47 PM</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>036</v>
+      </c>
+      <c r="B68" t="str">
+        <v>5/16/2026, 2:01:47 PM</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>038</v>
+      </c>
+      <c r="B69" t="str">
+        <v>5/16/2026, 2:02:47 PM</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>037</v>
+      </c>
+      <c r="B70" t="str">
+        <v>5/16/2026, 2:03:47 PM</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>036</v>
+      </c>
+      <c r="B71" t="str">
+        <v>5/16/2026, 2:04:47 PM</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>0236</v>
+      </c>
+      <c r="B72" t="str">
+        <v>5/16/2026, 2:05:47 PM</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>01</v>
+      </c>
+      <c r="B73" t="str">
+        <v>5/16/2026, 2:06:47 PM</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>153655</v>
+      </c>
+      <c r="B74" t="str">
+        <v>5/16/2026, 2:07:47 PM</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>035</v>
+      </c>
+      <c r="B75" t="str">
+        <v>5/16/2026, 2:08:47 PM</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>038</v>
+      </c>
+      <c r="B76" t="str">
+        <v>5/16/2026, 2:09:47 PM</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>036</v>
+      </c>
+      <c r="B77" t="str">
+        <v>5/16/2026, 2:10:47 PM</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>037</v>
+      </c>
+      <c r="B78" t="str">
+        <v>5/16/2026, 2:11:47 PM</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>0196</v>
+      </c>
+      <c r="B79" t="str">
+        <v>5/16/2026, 2:12:47 PM</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>01</v>
+      </c>
+      <c r="B80" t="str">
+        <v>5/16/2026, 2:13:47 PM</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>034</v>
+      </c>
+      <c r="B81" t="str">
+        <v>5/16/2026, 2:30:47 PM</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>034</v>
+      </c>
+      <c r="B82" t="str">
+        <v>5/16/2026, 2:31:47 PM</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>032</v>
+      </c>
+      <c r="B83" t="str">
+        <v>5/16/2026, 2:32:47 PM</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>087</v>
+      </c>
+      <c r="B84" t="str">
+        <v>5/16/2026, 2:33:47 PM</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>01</v>
+      </c>
+      <c r="B85" t="str">
+        <v>5/16/2026, 2:34:47 PM</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>1024202</v>
+      </c>
+      <c r="B86" t="str">
+        <v>5/16/2026, 2:35:47 PM</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>029</v>
+      </c>
+      <c r="B87" t="str">
+        <v>5/16/2026, 2:36:47 PM</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>031</v>
+      </c>
+      <c r="B88" t="str">
+        <v>5/16/2026, 2:37:47 PM</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>030</v>
+      </c>
+      <c r="B89" t="str">
+        <v>5/16/2026, 2:38:47 PM</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>030</v>
+      </c>
+      <c r="B90" t="str">
+        <v>5/16/2026, 2:39:47 PM</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>080</v>
+      </c>
+      <c r="B91" t="str">
+        <v>5/16/2026, 2:40:47 PM</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>01</v>
+      </c>
+      <c r="B92" t="str">
+        <v>5/16/2026, 2:41:47 PM</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>1024199</v>
+      </c>
+      <c r="B93" t="str">
+        <v>5/16/2026, 2:42:47 PM</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>028</v>
+      </c>
+      <c r="B94" t="str">
+        <v>5/16/2026, 2:43:47 PM</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>029</v>
+      </c>
+      <c r="B95" t="str">
+        <v>5/16/2026, 2:44:47 PM</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>030</v>
+      </c>
+      <c r="B96" t="str">
+        <v>5/16/2026, 2:45:47 PM</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>029</v>
+      </c>
+      <c r="B97" t="str">
+        <v>5/16/2026, 2:46:47 PM</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>089</v>
+      </c>
+      <c r="B98" t="str">
+        <v>5/16/2026, 2:47:47 PM</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>01</v>
+      </c>
+      <c r="B99" t="str">
+        <v>5/16/2026, 2:48:47 PM</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>128054</v>
+      </c>
+      <c r="B100" t="str">
+        <v>5/16/2026, 2:49:47 PM</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>026</v>
+      </c>
+      <c r="B101" t="str">
+        <v>5/16/2026, 2:50:47 PM</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>028</v>
+      </c>
+      <c r="B102" t="str">
+        <v>5/16/2026, 2:51:47 PM</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>028</v>
+      </c>
+      <c r="B103" t="str">
+        <v>5/16/2026, 2:52:47 PM</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>026</v>
+      </c>
+      <c r="B104" t="str">
+        <v>5/16/2026, 2:53:47 PM</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>0102</v>
+      </c>
+      <c r="B105" t="str">
+        <v>5/16/2026, 2:54:47 PM</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>01</v>
+      </c>
+      <c r="B106" t="str">
+        <v>5/16/2026, 2:55:47 PM</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>1280135</v>
+      </c>
+      <c r="B107" t="str">
+        <v>5/16/2026, 2:56:47 PM</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>025</v>
+      </c>
+      <c r="B108" t="str">
+        <v>5/16/2026, 2:57:47 PM</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>026</v>
+      </c>
+      <c r="B109" t="str">
+        <v>5/16/2026, 3:01:43 PM</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>027</v>
+      </c>
+      <c r="B110" t="str">
+        <v>5/16/2026, 3:02:43 PM</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>0103</v>
+      </c>
+      <c r="B111" t="str">
+        <v>5/16/2026, 3:03:52 PM</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>01</v>
+      </c>
+      <c r="B112" t="str">
+        <v>5/16/2026, 3:04:43 PM</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>1280246</v>
+      </c>
+      <c r="B113" t="str">
+        <v>5/16/2026, 3:05:43 PM</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>024</v>
+      </c>
+      <c r="B114" t="str">
+        <v>5/16/2026, 3:06:43 PM</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>026</v>
+      </c>
+      <c r="B115" t="str">
+        <v>5/16/2026, 3:07:43 PM</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>025</v>
+      </c>
+      <c r="B116" t="str">
+        <v>5/16/2026, 3:09:38 PM</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>025</v>
+      </c>
+      <c r="B117" t="str">
+        <v>5/16/2026, 3:09:43 PM</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>0101</v>
+      </c>
+      <c r="B118" t="str">
+        <v>5/16/2026, 3:10:43 PM</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>01</v>
+      </c>
+      <c r="B119" t="str">
+        <v>5/16/2026, 3:11:43 PM</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>153625</v>
+      </c>
+      <c r="B120" t="str">
+        <v>5/16/2026, 3:12:43 PM</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>024</v>
+      </c>
+      <c r="B121" t="str">
+        <v>5/16/2026, 3:13:43 PM</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>025</v>
+      </c>
+      <c r="B122" t="str">
+        <v>5/16/2026, 3:15:43 PM</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>025</v>
+      </c>
+      <c r="B123" t="str">
+        <v>5/16/2026, 3:16:43 PM</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B124" t="str">
+        <v>5/16/2026, 3:17:43 PM</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>01</v>
+      </c>
+      <c r="B125" t="str">
+        <v>5/16/2026, 3:18:43 PM</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>153646</v>
+      </c>
+      <c r="B126" t="str">
+        <v>5/16/2026, 3:19:43 PM</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>023</v>
+      </c>
+      <c r="B127" t="str">
+        <v>5/16/2026, 3:20:43 PM</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>024</v>
+      </c>
+      <c r="B128" t="str">
+        <v>5/16/2026, 3:22:43 PM</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>024</v>
+      </c>
+      <c r="B129" t="str">
+        <v>5/16/2026, 3:23:43 PM</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>0101</v>
+      </c>
+      <c r="B130" t="str">
+        <v>5/16/2026, 3:24:43 PM</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>01</v>
+      </c>
+      <c r="B131" t="str">
+        <v>5/16/2026, 3:25:43 PM</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>1536180</v>
+      </c>
+      <c r="B132" t="str">
+        <v>5/16/2026, 3:26:43 PM</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>023</v>
+      </c>
+      <c r="B133" t="str">
+        <v>5/16/2026, 3:27:43 PM</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>023</v>
+      </c>
+      <c r="B134" t="str">
+        <v>5/16/2026, 3:28:43 PM</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>024</v>
+      </c>
+      <c r="B135" t="str">
+        <v>5/16/2026, 3:29:43 PM</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>023</v>
+      </c>
+      <c r="B136" t="str">
+        <v>5/16/2026, 3:30:43 PM</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B137" t="str">
+        <v>5/16/2026, 3:31:43 PM</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>01</v>
+      </c>
+      <c r="B138" t="str">
+        <v>5/16/2026, 3:32:43 PM</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>17923</v>
+      </c>
+      <c r="B139" t="str">
+        <v>5/16/2026, 3:33:43 PM</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>023</v>
+      </c>
+      <c r="B140" t="str">
+        <v>5/16/2026, 3:34:43 PM</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>023</v>
+      </c>
+      <c r="B141" t="str">
+        <v>5/16/2026, 3:36:17 PM</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>024</v>
+      </c>
+      <c r="B142" t="str">
+        <v>5/16/2026, 3:37:17 PM</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>025</v>
+      </c>
+      <c r="B143" t="str">
+        <v>5/16/2026, 3:38:17 PM</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>024</v>
+      </c>
+      <c r="B144" t="str">
+        <v>5/16/2026, 3:39:17 PM</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>0103</v>
+      </c>
+      <c r="B145" t="str">
+        <v>5/16/2026, 3:40:16 PM</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>01</v>
+      </c>
+      <c r="B146" t="str">
+        <v>5/16/2026, 3:41:17 PM</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>179242</v>
+      </c>
+      <c r="B147" t="str">
+        <v>5/16/2026, 3:42:17 PM</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>024</v>
+      </c>
+      <c r="B148" t="str">
+        <v>5/16/2026, 3:43:17 PM</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>024</v>
+      </c>
+      <c r="B149" t="str">
+        <v>5/16/2026, 3:43:17 PM</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>025</v>
+      </c>
+      <c r="B150" t="str">
+        <v>5/16/2026, 3:44:17 PM</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>024</v>
+      </c>
+      <c r="B151" t="str">
+        <v>5/16/2026, 3:46:17 PM</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>098</v>
+      </c>
+      <c r="B152" t="str">
+        <v>5/16/2026, 3:47:17 PM</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>01</v>
+      </c>
+      <c r="B153" t="str">
+        <v>5/16/2026, 3:48:17 PM</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>1792126</v>
+      </c>
+      <c r="B154" t="str">
+        <v>5/16/2026, 3:49:17 PM</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>025</v>
+      </c>
+      <c r="B155" t="str">
+        <v>5/16/2026, 3:50:17 PM</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>026</v>
+      </c>
+      <c r="B156" t="str">
+        <v>5/16/2026, 3:51:17 PM</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>026</v>
+      </c>
+      <c r="B157" t="str">
+        <v>5/16/2026, 3:52:17 PM</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>024</v>
+      </c>
+      <c r="B158" t="str">
+        <v>5/16/2026, 3:53:17 PM</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>099</v>
+      </c>
+      <c r="B159" t="str">
+        <v>5/16/2026, 3:54:17 PM</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>024</v>
+      </c>
+      <c r="B160" t="str">
+        <v>5/16/2026, 4:05:17 PM</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>024</v>
+      </c>
+      <c r="B161" t="str">
+        <v>5/16/2026, 4:06:17 PM</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>025</v>
+      </c>
+      <c r="B162" t="str">
+        <v>5/16/2026, 4:07:24 PM</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>0101</v>
+      </c>
+      <c r="B163" t="str">
+        <v>5/16/2026, 4:08:17 PM</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>01</v>
+      </c>
+      <c r="B164" t="str">
+        <v>5/16/2026, 4:09:17 PM</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>17929</v>
+      </c>
+      <c r="B165" t="str">
+        <v>5/16/2026, 4:10:17 PM</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>025</v>
+      </c>
+      <c r="B166" t="str">
+        <v>5/16/2026, 4:11:17 PM</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>025</v>
+      </c>
+      <c r="B167" t="str">
+        <v>5/16/2026, 4:12:17 PM</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>026</v>
+      </c>
+      <c r="B168" t="str">
+        <v>5/16/2026, 4:13:17 PM</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>026</v>
+      </c>
+      <c r="B169" t="str">
+        <v>5/16/2026, 4:14:17 PM</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B170" t="str">
+        <v>5/16/2026, 4:15:17 PM</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>01</v>
+      </c>
+      <c r="B171" t="str">
+        <v>5/16/2026, 4:16:17 PM</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>179260</v>
+      </c>
+      <c r="B172" t="str">
+        <v>5/16/2026, 4:17:17 PM</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>024</v>
+      </c>
+      <c r="B173" t="str">
+        <v>5/16/2026, 4:18:17 PM</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>025</v>
+      </c>
+      <c r="B174" t="str">
+        <v>5/16/2026, 4:19:17 PM</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>025</v>
+      </c>
+      <c r="B175" t="str">
+        <v>5/16/2026, 4:20:17 PM</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>023</v>
+      </c>
+      <c r="B176" t="str">
+        <v>5/16/2026, 4:21:17 PM</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B177" t="str">
+        <v>5/16/2026, 4:22:17 PM</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>01</v>
+      </c>
+      <c r="B178" t="str">
+        <v>5/16/2026, 4:23:17 PM</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>179274</v>
+      </c>
+      <c r="B179" t="str">
+        <v>5/16/2026, 4:24:17 PM</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>023</v>
+      </c>
+      <c r="B180" t="str">
+        <v>5/16/2026, 4:25:17 PM</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>023</v>
+      </c>
+      <c r="B181" t="str">
+        <v>5/16/2026, 4:26:17 PM</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>023</v>
+      </c>
+      <c r="B182" t="str">
+        <v>5/16/2026, 4:27:17 PM</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>023</v>
+      </c>
+      <c r="B183" t="str">
+        <v>5/16/2026, 4:28:17 PM</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>087</v>
+      </c>
+      <c r="B184" t="str">
+        <v>5/16/2026, 4:29:17 PM</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>01</v>
+      </c>
+      <c r="B185" t="str">
+        <v>5/16/2026, 4:30:17 PM</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>179240</v>
+      </c>
+      <c r="B186" t="str">
+        <v>5/16/2026, 4:31:17 PM</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>022</v>
+      </c>
+      <c r="B187" t="str">
+        <v>5/16/2026, 4:32:17 PM</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>022</v>
+      </c>
+      <c r="B188" t="str">
+        <v>5/16/2026, 4:33:17 PM</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>022</v>
+      </c>
+      <c r="B189" t="str">
+        <v>5/16/2026, 4:34:17 PM</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>022</v>
+      </c>
+      <c r="B190" t="str">
+        <v>5/16/2026, 4:35:17 PM</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>070</v>
+      </c>
+      <c r="B191" t="str">
+        <v>5/16/2026, 4:36:17 PM</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>01</v>
+      </c>
+      <c r="B192" t="str">
+        <v>5/16/2026, 4:37:17 PM</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>179266</v>
+      </c>
+      <c r="B193" t="str">
+        <v>5/16/2026, 4:38:17 PM</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>021</v>
+      </c>
+      <c r="B194" t="str">
+        <v>5/16/2026, 4:39:17 PM</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>022</v>
+      </c>
+      <c r="B195" t="str">
+        <v>5/16/2026, 4:40:17 PM</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>022</v>
+      </c>
+      <c r="B196" t="str">
+        <v>5/16/2026, 4:41:17 PM</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>022</v>
+      </c>
+      <c r="B197" t="str">
+        <v>5/16/2026, 4:42:17 PM</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>060</v>
+      </c>
+      <c r="B198" t="str">
+        <v>5/16/2026, 4:43:17 PM</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>01</v>
+      </c>
+      <c r="B199" t="str">
+        <v>5/16/2026, 4:44:17 PM</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>1792105</v>
+      </c>
+      <c r="B200" t="str">
+        <v>5/16/2026, 4:45:17 PM</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>020</v>
+      </c>
+      <c r="B201" t="str">
+        <v>5/16/2026, 4:46:17 PM</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>022</v>
+      </c>
+      <c r="B202" t="str">
+        <v>5/16/2026, 4:47:17 PM</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>022</v>
+      </c>
+      <c r="B203" t="str">
+        <v>5/16/2026, 4:48:17 PM</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>023</v>
+      </c>
+      <c r="B204" t="str">
+        <v>5/16/2026, 4:49:17 PM</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>053</v>
+      </c>
+      <c r="B205" t="str">
+        <v>5/16/2026, 4:50:17 PM</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>01</v>
+      </c>
+      <c r="B206" t="str">
+        <v>5/16/2026, 4:51:17 PM</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>00</v>
+      </c>
+      <c r="B207" t="str">
+        <v>5/16/2026, 4:52:17 PM</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>020</v>
+      </c>
+      <c r="B208" t="str">
+        <v>5/16/2026, 4:53:17 PM</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>021</v>
+      </c>
+      <c r="B209" t="str">
+        <v>5/16/2026, 4:54:17 PM</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>021</v>
+      </c>
+      <c r="B210" t="str">
+        <v>5/16/2026, 4:55:17 PM</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>021</v>
+      </c>
+      <c r="B211" t="str">
+        <v>5/16/2026, 4:56:17 PM</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>030</v>
+      </c>
+      <c r="B212" t="str">
+        <v>5/16/2026, 4:57:51 PM</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>01</v>
+      </c>
+      <c r="B213" t="str">
+        <v>5/16/2026, 4:58:17 PM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B213"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B126"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -551,302 +4985,1014 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>00</v>
+        <v>058</v>
       </c>
       <c r="B2" t="str">
-        <v>7/7/2025, 11:49:50 am</v>
+        <v>1/29/2026, 11:34:16 AM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>019</v>
+        <v>058</v>
       </c>
       <c r="B3" t="str">
-        <v>7/7/2025, 11:58:50 am</v>
+        <v>1/29/2026, 11:34:16 AM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>019</v>
+        <v>058</v>
       </c>
       <c r="B4" t="str">
-        <v>7/7/2025, 11:59:50 am</v>
+        <v>1/29/2026, 11:34:17 AM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>020</v>
+        <v>058</v>
       </c>
       <c r="B5" t="str">
-        <v>7/7/2025, 12:00:50 pm</v>
+        <v>1/29/2026, 11:34:17 AM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>021</v>
+        <v>058</v>
       </c>
       <c r="B6" t="str">
-        <v>7/7/2025, 12:01:50 pm</v>
+        <v>1/29/2026, 11:34:18 AM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>01</v>
+        <v>060</v>
       </c>
       <c r="B7" t="str">
-        <v>7/7/2025, 12:03:50 pm</v>
+        <v>1/29/2026, 11:35:16 AM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>00</v>
+        <v>062</v>
       </c>
       <c r="B8" t="str">
-        <v>7/7/2025, 12:04:50 pm</v>
+        <v>1/29/2026, 11:36:16 AM</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>020</v>
+        <v>063</v>
       </c>
       <c r="B9" t="str">
-        <v>7/7/2025, 12:13:50 pm</v>
+        <v>1/29/2026, 11:37:16 AM</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>022</v>
+        <v>063</v>
       </c>
       <c r="B10" t="str">
-        <v>7/7/2025, 12:14:50 pm</v>
+        <v>1/29/2026, 11:37:16 AM</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>020</v>
+        <v>0101</v>
       </c>
       <c r="B11" t="str">
-        <v>7/7/2025, 12:15:50 pm</v>
+        <v>1/29/2026, 11:38:16 AM</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>020</v>
+        <v>0101</v>
       </c>
       <c r="B12" t="str">
-        <v>7/7/2025, 12:16:50 pm</v>
+        <v>1/29/2026, 11:38:16 AM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>032</v>
+        <v>01</v>
       </c>
       <c r="B13" t="str">
-        <v>7/7/2025, 12:17:50 pm</v>
+        <v>1/29/2026, 11:39:16 AM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>01</v>
+        <v>1280175</v>
       </c>
       <c r="B14" t="str">
-        <v>7/7/2025, 12:18:50 pm</v>
+        <v>1/29/2026, 11:40:16 AM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>01</v>
+        <v>057</v>
       </c>
       <c r="B15" t="str">
-        <v>7/7/2025, 12:18:50 pm</v>
+        <v>1/29/2026, 11:41:16 AM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>017</v>
+        <v>058</v>
       </c>
       <c r="B16" t="str">
-        <v>7/7/2025, 1:43:50 pm</v>
+        <v>1/29/2026, 11:42:16 AM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>017</v>
+        <v>058</v>
       </c>
       <c r="B17" t="str">
-        <v>7/7/2025, 1:44:50 pm</v>
+        <v>1/29/2026, 11:43:16 AM</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>018</v>
+        <v>058</v>
       </c>
       <c r="B18" t="str">
-        <v>7/7/2025, 1:45:50 pm</v>
+        <v>1/29/2026, 11:43:16 AM</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>018</v>
+        <v>058</v>
       </c>
       <c r="B19" t="str">
-        <v>7/7/2025, 1:45:50 pm</v>
+        <v>1/29/2026, 11:43:17 AM</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>069</v>
+        <v>058</v>
       </c>
       <c r="B20" t="str">
-        <v>7/7/2025, 1:47:50 pm</v>
+        <v>1/29/2026, 11:43:17 AM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>017</v>
+        <v>058</v>
       </c>
       <c r="B21" t="str">
-        <v>7/7/2025, 1:58:50 pm</v>
+        <v>1/29/2026, 11:43:18 AM</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>018</v>
+        <v>058</v>
       </c>
       <c r="B22" t="str">
-        <v>7/7/2025, 1:59:50 pm</v>
+        <v>1/29/2026, 11:44:16 AM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>020</v>
+        <v>0101</v>
       </c>
       <c r="B23" t="str">
-        <v>7/7/2025, 2:00:50 pm</v>
+        <v>1/29/2026, 11:45:16 AM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>088</v>
+        <v>01</v>
       </c>
       <c r="B24" t="str">
-        <v>7/7/2025, 2:02:50 pm</v>
+        <v>1/29/2026, 11:46:16 AM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>01</v>
+        <v>15361</v>
       </c>
       <c r="B25" t="str">
-        <v>7/7/2025, 2:03:50 pm</v>
+        <v>1/29/2026, 11:47:16 AM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>01</v>
+        <v>057</v>
       </c>
       <c r="B26" t="str">
-        <v>7/7/2025, 2:03:50 pm</v>
+        <v>1/29/2026, 11:48:16 AM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>022</v>
+        <v>057</v>
       </c>
       <c r="B27" t="str">
-        <v>7/7/2025, 3:15:50 pm</v>
+        <v>1/29/2026, 11:49:16 AM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>025</v>
+        <v>058</v>
       </c>
       <c r="B28" t="str">
-        <v>7/7/2025, 3:16:50 pm</v>
+        <v>1/29/2026, 11:50:16 AM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>01</v>
+        <v>058</v>
       </c>
       <c r="B29" t="str">
-        <v>7/7/2025, 3:18:50 pm</v>
+        <v>1/29/2026, 11:50:16 AM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>00</v>
+        <v>058</v>
       </c>
       <c r="B30" t="str">
-        <v>7/7/2025, 3:19:59 pm</v>
+        <v>1/29/2026, 11:50:17 AM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>024</v>
+        <v>058</v>
       </c>
       <c r="B31" t="str">
-        <v>7/7/2025, 3:28:50 pm</v>
+        <v>1/29/2026, 11:51:16 AM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>025</v>
+        <v>058</v>
       </c>
       <c r="B32" t="str">
-        <v>7/7/2025, 3:29:50 pm</v>
+        <v>1/29/2026, 11:51:17 AM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>025</v>
+        <v>01</v>
       </c>
       <c r="B33" t="str">
-        <v>7/7/2025, 3:30:50 pm</v>
+        <v>1/29/2026, 11:53:16 AM</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>025</v>
+        <v>153688</v>
       </c>
       <c r="B34" t="str">
-        <v>7/7/2025, 3:30:51 pm</v>
+        <v>1/29/2026, 11:54:16 AM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>026</v>
+        <v>055</v>
       </c>
       <c r="B35" t="str">
-        <v>7/7/2025, 3:31:50 pm</v>
+        <v>1/29/2026, 11:55:16 AM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>053</v>
+        <v>061</v>
       </c>
       <c r="B36" t="str">
-        <v>7/7/2025, 3:32:50 pm</v>
+        <v>1/29/2026, 11:56:16 AM</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>01</v>
+        <v>060</v>
       </c>
       <c r="B37" t="str">
-        <v>7/7/2025, 3:33:50 pm</v>
+        <v>1/29/2026, 11:57:16 AM</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>064</v>
+      </c>
+      <c r="B38" t="str">
+        <v>1/29/2026, 11:58:16 AM</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>064</v>
+      </c>
+      <c r="B39" t="str">
+        <v>1/29/2026, 11:58:16 AM</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>0104</v>
+      </c>
+      <c r="B40" t="str">
+        <v>1/29/2026, 11:59:16 AM</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>0104</v>
+      </c>
+      <c r="B41" t="str">
+        <v>1/29/2026, 11:59:16 AM</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>01</v>
+      </c>
+      <c r="B42" t="str">
+        <v>1/29/2026, 12:00:16 PM</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>01</v>
+      </c>
+      <c r="B43" t="str">
+        <v>1/29/2026, 12:00:17 PM</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>01</v>
+      </c>
+      <c r="B44" t="str">
+        <v>1/29/2026, 12:00:17 PM</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>1536187</v>
+      </c>
+      <c r="B45" t="str">
+        <v>1/29/2026, 12:01:16 PM</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>061</v>
+      </c>
+      <c r="B46" t="str">
+        <v>1/29/2026, 12:02:16 PM</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>069</v>
+      </c>
+      <c r="B47" t="str">
+        <v>1/29/2026, 12:03:16 PM</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>071</v>
+      </c>
+      <c r="B48" t="str">
+        <v>1/29/2026, 12:04:16 PM</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>071</v>
+      </c>
+      <c r="B49" t="str">
+        <v>1/29/2026, 12:04:16 PM</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>079</v>
+      </c>
+      <c r="B50" t="str">
+        <v>1/29/2026, 12:05:16 PM</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>0113</v>
+      </c>
+      <c r="B51" t="str">
+        <v>1/29/2026, 12:06:16 PM</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>0113</v>
+      </c>
+      <c r="B52" t="str">
+        <v>1/29/2026, 12:06:16 PM</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>0113</v>
+      </c>
+      <c r="B53" t="str">
+        <v>1/29/2026, 12:06:17 PM</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>0113</v>
+      </c>
+      <c r="B54" t="str">
+        <v>1/29/2026, 12:06:17 PM</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>01</v>
+      </c>
+      <c r="B55" t="str">
+        <v>1/29/2026, 12:07:16 PM</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>01</v>
+      </c>
+      <c r="B56" t="str">
+        <v>1/29/2026, 12:07:17 PM</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>179212</v>
+      </c>
+      <c r="B57" t="str">
+        <v>1/29/2026, 12:08:16 PM</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>067</v>
+      </c>
+      <c r="B58" t="str">
+        <v>1/29/2026, 12:09:16 PM</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>067</v>
+      </c>
+      <c r="B59" t="str">
+        <v>1/29/2026, 12:09:16 PM</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>067</v>
+      </c>
+      <c r="B60" t="str">
+        <v>1/29/2026, 12:09:17 PM</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>071</v>
+      </c>
+      <c r="B61" t="str">
+        <v>1/29/2026, 12:10:16 PM</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>071</v>
+      </c>
+      <c r="B62" t="str">
+        <v>1/29/2026, 12:10:17 PM</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>070</v>
+      </c>
+      <c r="B63" t="str">
+        <v>1/29/2026, 12:11:16 PM</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>065</v>
+      </c>
+      <c r="B64" t="str">
+        <v>1/29/2026, 12:12:16 PM</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>256234</v>
+      </c>
+      <c r="B65" t="str">
+        <v>1/29/2026, 12:13:16 PM</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>01</v>
+      </c>
+      <c r="B66" t="str">
+        <v>1/29/2026, 12:14:16 PM</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>01</v>
+      </c>
+      <c r="B67" t="str">
+        <v>1/29/2026, 12:14:16 PM</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>01</v>
+      </c>
+      <c r="B68" t="str">
+        <v>1/29/2026, 12:14:17 PM</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>01</v>
+      </c>
+      <c r="B69" t="str">
+        <v>1/29/2026, 12:14:17 PM</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>01</v>
+      </c>
+      <c r="B70" t="str">
+        <v>1/29/2026, 12:14:18 PM</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>1792108</v>
+      </c>
+      <c r="B71" t="str">
+        <v>1/29/2026, 12:15:16 PM</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>060</v>
+      </c>
+      <c r="B72" t="str">
+        <v>1/29/2026, 12:16:16 PM</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>060</v>
+      </c>
+      <c r="B73" t="str">
+        <v>1/29/2026, 12:16:16 PM</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>060</v>
+      </c>
+      <c r="B74" t="str">
+        <v>1/29/2026, 12:16:17 PM</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>064</v>
+      </c>
+      <c r="B75" t="str">
+        <v>1/29/2026, 12:17:16 PM</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>064</v>
+      </c>
+      <c r="B76" t="str">
+        <v>1/29/2026, 12:17:16 PM</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>064</v>
+      </c>
+      <c r="B77" t="str">
+        <v>1/29/2026, 12:17:17 PM</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>068</v>
+      </c>
+      <c r="B78" t="str">
+        <v>1/29/2026, 12:19:17 PM</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>068</v>
+      </c>
+      <c r="B79" t="str">
+        <v>1/29/2026, 12:19:17 PM</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>068</v>
+      </c>
+      <c r="B80" t="str">
+        <v>1/29/2026, 12:19:17 PM</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>068</v>
+      </c>
+      <c r="B81" t="str">
+        <v>1/29/2026, 12:19:18 PM</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>068</v>
+      </c>
+      <c r="B82" t="str">
+        <v>1/29/2026, 12:19:20 PM</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>256167</v>
+      </c>
+      <c r="B83" t="str">
+        <v>1/29/2026, 12:20:16 PM</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>256167</v>
+      </c>
+      <c r="B84" t="str">
+        <v>1/29/2026, 12:20:16 PM</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>01</v>
+      </c>
+      <c r="B85" t="str">
+        <v>1/29/2026, 12:21:16 PM</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>1792103</v>
+      </c>
+      <c r="B86" t="str">
+        <v>1/29/2026, 12:22:16 PM</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>064</v>
+      </c>
+      <c r="B87" t="str">
+        <v>1/29/2026, 12:23:16 PM</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>064</v>
+      </c>
+      <c r="B88" t="str">
+        <v>1/29/2026, 12:23:17 PM</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>064</v>
+      </c>
+      <c r="B89" t="str">
+        <v>1/29/2026, 12:23:17 PM</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>070</v>
+      </c>
+      <c r="B90" t="str">
+        <v>1/29/2026, 12:24:16 PM</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>068</v>
+      </c>
+      <c r="B91" t="str">
+        <v>1/29/2026, 12:25:16 PM</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>067</v>
+      </c>
+      <c r="B92" t="str">
+        <v>1/29/2026, 12:26:16 PM</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>25667</v>
+      </c>
+      <c r="B93" t="str">
+        <v>1/29/2026, 12:27:16 PM</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>25667</v>
+      </c>
+      <c r="B94" t="str">
+        <v>1/29/2026, 12:27:17 PM</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>25667</v>
+      </c>
+      <c r="B95" t="str">
+        <v>1/29/2026, 12:27:17 PM</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>25667</v>
+      </c>
+      <c r="B96" t="str">
+        <v>1/29/2026, 12:27:17 PM</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>25667</v>
+      </c>
+      <c r="B97" t="str">
+        <v>1/29/2026, 12:27:18 PM</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>25667</v>
+      </c>
+      <c r="B98" t="str">
+        <v>1/29/2026, 12:27:20 PM</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>01</v>
+      </c>
+      <c r="B99" t="str">
+        <v>1/29/2026, 12:28:16 PM</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>153622</v>
+      </c>
+      <c r="B100" t="str">
+        <v>1/29/2026, 12:29:16 PM</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>069</v>
+      </c>
+      <c r="B101" t="str">
+        <v>1/29/2026, 12:30:16 PM</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>069</v>
+      </c>
+      <c r="B102" t="str">
+        <v>1/29/2026, 12:30:17 PM</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>071</v>
+      </c>
+      <c r="B103" t="str">
+        <v>1/29/2026, 12:31:16 PM</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>068</v>
+      </c>
+      <c r="B104" t="str">
+        <v>1/29/2026, 12:32:16 PM</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>071</v>
+      </c>
+      <c r="B105" t="str">
+        <v>1/29/2026, 12:33:16 PM</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>070</v>
+      </c>
+      <c r="B106" t="str">
+        <v>1/29/2026, 12:37:16 PM</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>070</v>
+      </c>
+      <c r="B107" t="str">
+        <v>1/29/2026, 12:38:16 PM</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>070</v>
+      </c>
+      <c r="B108" t="str">
+        <v>1/29/2026, 12:38:17 PM</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>070</v>
+      </c>
+      <c r="B109" t="str">
+        <v>1/29/2026, 12:38:17 PM</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>070</v>
+      </c>
+      <c r="B110" t="str">
+        <v>1/29/2026, 12:39:16 PM</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>071</v>
+      </c>
+      <c r="B111" t="str">
+        <v>1/29/2026, 12:40:16 PM</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>071</v>
+      </c>
+      <c r="B112" t="str">
+        <v>1/29/2026, 12:40:17 PM</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>0174</v>
+      </c>
+      <c r="B113" t="str">
+        <v>1/29/2026, 12:41:16 PM</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>01</v>
+      </c>
+      <c r="B114" t="str">
+        <v>1/29/2026, 12:42:16 PM</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>1024153</v>
+      </c>
+      <c r="B115" t="str">
+        <v>1/29/2026, 12:43:16 PM</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>1024153</v>
+      </c>
+      <c r="B116" t="str">
+        <v>1/29/2026, 12:43:17 PM</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>068</v>
+      </c>
+      <c r="B117" t="str">
+        <v>1/29/2026, 12:44:16 PM</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>068</v>
+      </c>
+      <c r="B118" t="str">
+        <v>1/29/2026, 12:44:17 PM</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>070</v>
+      </c>
+      <c r="B119" t="str">
+        <v>1/29/2026, 12:45:16 PM</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>070</v>
+      </c>
+      <c r="B120" t="str">
+        <v>1/29/2026, 12:45:17 PM</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>070</v>
+      </c>
+      <c r="B121" t="str">
+        <v>1/29/2026, 12:45:17 PM</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>072</v>
+      </c>
+      <c r="B122" t="str">
+        <v>1/29/2026, 12:46:16 PM</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>072</v>
+      </c>
+      <c r="B123" t="str">
+        <v>1/29/2026, 12:46:17 PM</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>072</v>
+      </c>
+      <c r="B124" t="str">
+        <v>1/29/2026, 12:46:17 PM</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>072</v>
+      </c>
+      <c r="B125" t="str">
+        <v>1/29/2026, 12:46:17 PM</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>072</v>
+      </c>
+      <c r="B126" t="str">
+        <v>1/29/2026, 12:47:16 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B126"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -858,70 +6004,78 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>6400153</v>
+        <v>1024157</v>
       </c>
       <c r="B2" t="str">
-        <v>26/11/2025, 3:50:09 pm</v>
+        <v>1/30/2026, 11:34:41 PM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>6400153</v>
+        <v>1024157</v>
       </c>
       <c r="B3" t="str">
-        <v>26/11/2025, 3:51:09 pm</v>
+        <v>1/30/2026, 11:34:42 PM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>5632146</v>
+        <v>015</v>
       </c>
       <c r="B4" t="str">
-        <v>26/11/2025, 3:53:18 pm</v>
+        <v>1/30/2026, 11:35:41 PM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>5632146</v>
+        <v>015</v>
       </c>
       <c r="B5" t="str">
-        <v>26/11/2025, 3:53:18 pm</v>
+        <v>1/30/2026, 11:36:41 PM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>588898</v>
+        <v>016</v>
       </c>
       <c r="B6" t="str">
-        <v>26/11/2025, 3:56:35 pm</v>
+        <v>1/30/2026, 11:37:41 PM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>5632226</v>
+        <v>016</v>
       </c>
       <c r="B7" t="str">
-        <v>26/11/2025, 4:00:21 pm</v>
+        <v>1/30/2026, 11:37:42 PM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0185</v>
+        <v>017</v>
       </c>
       <c r="B8" t="str">
-        <v>26/11/2025, 5:38:46 pm</v>
+        <v>1/30/2026, 11:38:41 PM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B9" t="str">
+        <v>1/30/2026, 11:39:41 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B163"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -933,343 +6087,2822 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>01</v>
+        <v>08</v>
       </c>
       <c r="B2" t="str">
-        <v>27/11/2025, 12:06:37 pm</v>
+        <v>1/31/2026, 12:30:08 PM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>01</v>
+        <v>014</v>
       </c>
       <c r="B3" t="str">
-        <v>27/11/2025, 12:06:37 pm</v>
+        <v>1/31/2026, 12:31:08 PM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>092</v>
+        <v>014</v>
       </c>
       <c r="B4" t="str">
-        <v>27/11/2025, 12:57:07 pm</v>
+        <v>1/31/2026, 12:31:08 PM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>096</v>
+        <v>014</v>
       </c>
       <c r="B5" t="str">
-        <v>27/11/2025, 12:58:07 pm</v>
+        <v>1/31/2026, 12:32:08 PM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>096</v>
+        <v>014</v>
       </c>
       <c r="B6" t="str">
-        <v>27/11/2025, 12:58:07 pm</v>
+        <v>1/31/2026, 12:32:08 PM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>096</v>
+        <v>015</v>
       </c>
       <c r="B7" t="str">
-        <v>27/11/2025, 12:59:07 pm</v>
+        <v>1/31/2026, 12:33:08 PM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>096</v>
+        <v>013</v>
       </c>
       <c r="B8" t="str">
-        <v>27/11/2025, 1:00:07 pm</v>
+        <v>1/31/2026, 12:35:15 PM</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>0106</v>
+        <v>013</v>
       </c>
       <c r="B9" t="str">
-        <v>27/11/2025, 1:01:07 pm</v>
+        <v>1/31/2026, 12:36:15 PM</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>0106</v>
+        <v>013</v>
       </c>
       <c r="B10" t="str">
-        <v>27/11/2025, 1:01:07 pm</v>
+        <v>1/31/2026, 12:37:15 PM</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>01</v>
+        <v>013</v>
       </c>
       <c r="B11" t="str">
-        <v>27/11/2025, 1:02:07 pm</v>
+        <v>1/31/2026, 12:38:16 PM</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>00</v>
+        <v>013</v>
       </c>
       <c r="B12" t="str">
-        <v>27/11/2025, 1:03:07 pm</v>
+        <v>1/31/2026, 12:38:16 PM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>00</v>
+        <v>0107</v>
       </c>
       <c r="B13" t="str">
-        <v>27/11/2025, 1:03:07 pm</v>
+        <v>1/31/2026, 12:39:15 PM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>090</v>
+        <v>01</v>
       </c>
       <c r="B14" t="str">
-        <v>27/11/2025, 1:35:29 pm</v>
+        <v>1/31/2026, 12:40:15 PM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>096</v>
+        <v>011</v>
       </c>
       <c r="B15" t="str">
-        <v>27/11/2025, 1:36:29 pm</v>
+        <v>1/31/2026, 12:44:15 PM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>096</v>
+        <v>011</v>
       </c>
       <c r="B16" t="str">
-        <v>27/11/2025, 1:36:29 pm</v>
+        <v>1/31/2026, 12:45:15 PM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>01</v>
+        <v>011</v>
       </c>
       <c r="B17" t="str">
-        <v>27/11/2025, 1:37:29 pm</v>
+        <v>1/31/2026, 12:45:16 PM</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>00</v>
+        <v>011</v>
       </c>
       <c r="B18" t="str">
-        <v>27/11/2025, 1:38:29 pm</v>
+        <v>1/31/2026, 12:45:16 PM</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>078</v>
+        <v>097</v>
       </c>
       <c r="B19" t="str">
-        <v>27/11/2025, 1:46:34 pm</v>
+        <v>1/31/2026, 12:46:15 PM</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>081</v>
+        <v>01</v>
       </c>
       <c r="B20" t="str">
-        <v>27/11/2025, 1:47:29 pm</v>
+        <v>1/31/2026, 12:47:15 PM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>081</v>
+        <v>179297</v>
       </c>
       <c r="B21" t="str">
-        <v>27/11/2025, 1:47:29 pm</v>
+        <v>1/31/2026, 12:48:15 PM</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>083</v>
+        <v>096</v>
       </c>
       <c r="B22" t="str">
-        <v>27/11/2025, 1:48:34 pm</v>
+        <v>1/31/2026, 12:53:15 PM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>083</v>
+        <v>096</v>
       </c>
       <c r="B23" t="str">
-        <v>27/11/2025, 1:48:34 pm</v>
+        <v>1/31/2026, 12:53:16 PM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>081</v>
+        <v>01</v>
       </c>
       <c r="B24" t="str">
-        <v>27/11/2025, 1:49:29 pm</v>
+        <v>1/31/2026, 12:54:15 PM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>0107</v>
+        <v>01</v>
       </c>
       <c r="B25" t="str">
-        <v>27/11/2025, 1:50:29 pm</v>
+        <v>1/31/2026, 12:54:16 PM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>01</v>
+        <v>179278</v>
       </c>
       <c r="B26" t="str">
-        <v>27/11/2025, 1:51:29 pm</v>
+        <v>1/31/2026, 12:55:15 PM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>00</v>
+        <v>013</v>
       </c>
       <c r="B27" t="str">
-        <v>27/11/2025, 1:52:29 pm</v>
+        <v>1/31/2026, 12:56:15 PM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>073</v>
+        <v>015</v>
       </c>
       <c r="B28" t="str">
-        <v>27/11/2025, 1:54:18 pm</v>
+        <v>1/31/2026, 12:57:15 PM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>073</v>
+        <v>015</v>
       </c>
       <c r="B29" t="str">
-        <v>27/11/2025, 1:54:19 pm</v>
+        <v>1/31/2026, 12:57:16 PM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>073</v>
+        <v>014</v>
       </c>
       <c r="B30" t="str">
-        <v>27/11/2025, 1:54:19 pm</v>
+        <v>1/31/2026, 12:58:15 PM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>073</v>
+        <v>014</v>
       </c>
       <c r="B31" t="str">
-        <v>27/11/2025, 1:54:19 pm</v>
+        <v>1/31/2026, 12:59:15 PM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>073</v>
+        <v>014</v>
       </c>
       <c r="B32" t="str">
-        <v>27/11/2025, 1:54:20 pm</v>
+        <v>1/31/2026, 12:59:16 PM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>079</v>
+        <v>095</v>
       </c>
       <c r="B33" t="str">
-        <v>27/11/2025, 1:55:18 pm</v>
+        <v>1/31/2026, 1:00:15 PM</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>079</v>
+        <v>01</v>
       </c>
       <c r="B34" t="str">
-        <v>27/11/2025, 1:55:19 pm</v>
+        <v>1/31/2026, 1:01:15 PM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>077</v>
+        <v>01</v>
       </c>
       <c r="B35" t="str">
-        <v>27/11/2025, 1:56:18 pm</v>
+        <v>1/31/2026, 1:01:16 PM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>077</v>
+        <v>1536147</v>
       </c>
       <c r="B36" t="str">
-        <v>27/11/2025, 1:58:03 pm</v>
+        <v>1/31/2026, 1:02:15 PM</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>077</v>
+        <v>017</v>
       </c>
       <c r="B37" t="str">
-        <v>27/11/2025, 1:58:03 pm</v>
+        <v>1/31/2026, 1:17:15 PM</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>077</v>
+        <v>017</v>
       </c>
       <c r="B38" t="str">
-        <v>27/11/2025, 1:58:04 pm</v>
+        <v>1/31/2026, 1:17:16 PM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>077</v>
+        <v>017</v>
       </c>
       <c r="B39" t="str">
-        <v>27/11/2025, 1:58:05 pm</v>
+        <v>1/31/2026, 1:18:15 PM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>075</v>
+        <v>017</v>
       </c>
       <c r="B40" t="str">
-        <v>27/11/2025, 2:01:44 pm</v>
+        <v>1/31/2026, 1:18:16 PM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>075</v>
+        <v>017</v>
       </c>
       <c r="B41" t="str">
-        <v>27/11/2025, 2:01:45 pm</v>
+        <v>1/31/2026, 1:18:16 PM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>075</v>
+        <v>017</v>
       </c>
       <c r="B42" t="str">
-        <v>27/11/2025, 2:01:45 pm</v>
+        <v>1/31/2026, 1:18:16 PM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>075</v>
+        <v>017</v>
       </c>
       <c r="B43" t="str">
-        <v>27/11/2025, 2:01:45 pm</v>
+        <v>1/31/2026, 1:19:15 PM</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>018</v>
+      </c>
+      <c r="B44" t="str">
+        <v>1/31/2026, 1:20:15 PM</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>098</v>
+      </c>
+      <c r="B45" t="str">
+        <v>1/31/2026, 1:21:15 PM</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>01</v>
+      </c>
+      <c r="B46" t="str">
+        <v>1/31/2026, 1:22:15 PM</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>128093</v>
+      </c>
+      <c r="B47" t="str">
+        <v>1/31/2026, 1:23:15 PM</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>128093</v>
+      </c>
+      <c r="B48" t="str">
+        <v>1/31/2026, 1:23:16 PM</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>128093</v>
+      </c>
+      <c r="B49" t="str">
+        <v>1/31/2026, 1:23:16 PM</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>128093</v>
+      </c>
+      <c r="B50" t="str">
+        <v>1/31/2026, 1:23:16 PM</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>016</v>
+      </c>
+      <c r="B51" t="str">
+        <v>1/31/2026, 1:24:15 PM</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>017</v>
+      </c>
+      <c r="B52" t="str">
+        <v>1/31/2026, 1:25:15 PM</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>018</v>
+      </c>
+      <c r="B53" t="str">
+        <v>1/31/2026, 1:26:15 PM</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>018</v>
+      </c>
+      <c r="B54" t="str">
+        <v>1/31/2026, 1:27:15 PM</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>018</v>
+      </c>
+      <c r="B55" t="str">
+        <v>1/31/2026, 1:27:16 PM</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>018</v>
+      </c>
+      <c r="B56" t="str">
+        <v>1/31/2026, 1:27:16 PM</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>089</v>
+      </c>
+      <c r="B57" t="str">
+        <v>1/31/2026, 1:28:15 PM</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>01</v>
+      </c>
+      <c r="B58" t="str">
+        <v>1/31/2026, 1:29:15 PM</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>01</v>
+      </c>
+      <c r="B59" t="str">
+        <v>1/31/2026, 1:29:16 PM</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>128029</v>
+      </c>
+      <c r="B60" t="str">
+        <v>1/31/2026, 1:30:15 PM</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>017</v>
+      </c>
+      <c r="B61" t="str">
+        <v>1/31/2026, 1:31:15 PM</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>018</v>
+      </c>
+      <c r="B62" t="str">
+        <v>1/31/2026, 1:32:15 PM</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>018</v>
+      </c>
+      <c r="B63" t="str">
+        <v>1/31/2026, 1:33:15 PM</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>018</v>
+      </c>
+      <c r="B64" t="str">
+        <v>1/31/2026, 1:34:15 PM</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>018</v>
+      </c>
+      <c r="B65" t="str">
+        <v>1/31/2026, 1:34:16 PM</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>018</v>
+      </c>
+      <c r="B66" t="str">
+        <v>1/31/2026, 1:34:16 PM</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>062</v>
+      </c>
+      <c r="B67" t="str">
+        <v>1/31/2026, 1:35:15 PM</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>062</v>
+      </c>
+      <c r="B68" t="str">
+        <v>1/31/2026, 1:35:16 PM</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>062</v>
+      </c>
+      <c r="B69" t="str">
+        <v>1/31/2026, 1:35:16 PM</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>062</v>
+      </c>
+      <c r="B70" t="str">
+        <v>1/31/2026, 1:35:16 PM</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>062</v>
+      </c>
+      <c r="B71" t="str">
+        <v>1/31/2026, 1:35:17 PM</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>01</v>
+      </c>
+      <c r="B72" t="str">
+        <v>1/31/2026, 1:36:15 PM</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>01</v>
+      </c>
+      <c r="B73" t="str">
+        <v>1/31/2026, 1:36:16 PM</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>1024234</v>
+      </c>
+      <c r="B74" t="str">
+        <v>1/31/2026, 1:37:15 PM</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>017</v>
+      </c>
+      <c r="B75" t="str">
+        <v>1/31/2026, 1:38:15 PM</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>017</v>
+      </c>
+      <c r="B76" t="str">
+        <v>1/31/2026, 1:38:16 PM</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>017</v>
+      </c>
+      <c r="B77" t="str">
+        <v>1/31/2026, 1:38:16 PM</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>017</v>
+      </c>
+      <c r="B78" t="str">
+        <v>1/31/2026, 1:39:15 PM</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>018</v>
+      </c>
+      <c r="B79" t="str">
+        <v>1/31/2026, 1:40:15 PM</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>017</v>
+      </c>
+      <c r="B80" t="str">
+        <v>1/31/2026, 1:41:15 PM</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>056</v>
+      </c>
+      <c r="B81" t="str">
+        <v>1/31/2026, 1:42:15 PM</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>01</v>
+      </c>
+      <c r="B82" t="str">
+        <v>1/31/2026, 1:43:15 PM</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>1024168</v>
+      </c>
+      <c r="B83" t="str">
+        <v>1/31/2026, 1:44:15 PM</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>015</v>
+      </c>
+      <c r="B84" t="str">
+        <v>1/31/2026, 1:45:15 PM</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>017</v>
+      </c>
+      <c r="B85" t="str">
+        <v>1/31/2026, 1:46:15 PM</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>017</v>
+      </c>
+      <c r="B86" t="str">
+        <v>1/31/2026, 1:46:16 PM</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>017</v>
+      </c>
+      <c r="B87" t="str">
+        <v>1/31/2026, 1:47:15 PM</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>017</v>
+      </c>
+      <c r="B88" t="str">
+        <v>1/31/2026, 1:48:15 PM</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>017</v>
+      </c>
+      <c r="B89" t="str">
+        <v>1/31/2026, 1:48:16 PM</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>065</v>
+      </c>
+      <c r="B90" t="str">
+        <v>1/31/2026, 1:49:15 PM</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>01</v>
+      </c>
+      <c r="B91" t="str">
+        <v>1/31/2026, 1:50:15 PM</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>1024164</v>
+      </c>
+      <c r="B92" t="str">
+        <v>1/31/2026, 1:51:15 PM</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>1024164</v>
+      </c>
+      <c r="B93" t="str">
+        <v>1/31/2026, 1:51:16 PM</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>017</v>
+      </c>
+      <c r="B94" t="str">
+        <v>1/31/2026, 1:52:15 PM</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>017</v>
+      </c>
+      <c r="B95" t="str">
+        <v>1/31/2026, 1:53:15 PM</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>017</v>
+      </c>
+      <c r="B96" t="str">
+        <v>1/31/2026, 1:54:15 PM</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>016</v>
+      </c>
+      <c r="B97" t="str">
+        <v>1/31/2026, 1:55:15 PM</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>092</v>
+      </c>
+      <c r="B98" t="str">
+        <v>1/31/2026, 1:56:15 PM</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>092</v>
+      </c>
+      <c r="B99" t="str">
+        <v>1/31/2026, 1:56:16 PM</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>01</v>
+      </c>
+      <c r="B100" t="str">
+        <v>1/31/2026, 1:57:15 PM</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>1024213</v>
+      </c>
+      <c r="B101" t="str">
+        <v>1/31/2026, 1:58:15 PM</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>1024213</v>
+      </c>
+      <c r="B102" t="str">
+        <v>1/31/2026, 1:58:16 PM</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>1024213</v>
+      </c>
+      <c r="B103" t="str">
+        <v>1/31/2026, 1:58:16 PM</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>017</v>
+      </c>
+      <c r="B104" t="str">
+        <v>1/31/2026, 1:59:16 PM</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>016</v>
+      </c>
+      <c r="B105" t="str">
+        <v>1/31/2026, 2:00:15 PM</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>016</v>
+      </c>
+      <c r="B106" t="str">
+        <v>1/31/2026, 2:01:15 PM</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>016</v>
+      </c>
+      <c r="B107" t="str">
+        <v>1/31/2026, 2:01:16 PM</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>017</v>
+      </c>
+      <c r="B108" t="str">
+        <v>1/31/2026, 2:02:15 PM</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>0144</v>
+      </c>
+      <c r="B109" t="str">
+        <v>1/31/2026, 2:03:15 PM</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>01</v>
+      </c>
+      <c r="B110" t="str">
+        <v>1/31/2026, 2:04:15 PM</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B111" t="str">
+        <v>1/31/2026, 9:04:38 PM</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B112" t="str">
+        <v>1/31/2026, 9:04:38 PM</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>0193</v>
+      </c>
+      <c r="B113" t="str">
+        <v>1/31/2026, 9:05:38 PM</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>0193</v>
+      </c>
+      <c r="B114" t="str">
+        <v>1/31/2026, 9:05:38 PM</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>0193</v>
+      </c>
+      <c r="B115" t="str">
+        <v>1/31/2026, 9:05:39 PM</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B116" t="str">
+        <v>1/31/2026, 9:06:38 PM</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B117" t="str">
+        <v>1/31/2026, 9:07:38 PM</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B118" t="str">
+        <v>1/31/2026, 9:07:38 PM</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B119" t="str">
+        <v>1/31/2026, 9:07:39 PM</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>0100</v>
+      </c>
+      <c r="B120" t="str">
+        <v>1/31/2026, 9:07:39 PM</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>01</v>
+      </c>
+      <c r="B121" t="str">
+        <v>1/31/2026, 9:08:38 PM</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>1024166</v>
+      </c>
+      <c r="B122" t="str">
+        <v>1/31/2026, 9:09:38 PM</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>0184</v>
+      </c>
+      <c r="B123" t="str">
+        <v>1/31/2026, 9:10:38 PM</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>0193</v>
+      </c>
+      <c r="B124" t="str">
+        <v>1/31/2026, 9:11:38 PM</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>0189</v>
+      </c>
+      <c r="B125" t="str">
+        <v>1/31/2026, 9:12:38 PM</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>0192</v>
+      </c>
+      <c r="B126" t="str">
+        <v>1/31/2026, 9:13:38 PM</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>093</v>
+      </c>
+      <c r="B127" t="str">
+        <v>1/31/2026, 9:14:38 PM</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>01</v>
+      </c>
+      <c r="B128" t="str">
+        <v>1/31/2026, 9:15:38 PM</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>01</v>
+      </c>
+      <c r="B129" t="str">
+        <v>1/31/2026, 9:15:38 PM</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>1024147</v>
+      </c>
+      <c r="B130" t="str">
+        <v>1/31/2026, 9:16:38 PM</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>0186</v>
+      </c>
+      <c r="B131" t="str">
+        <v>1/31/2026, 9:17:38 PM</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>0201</v>
+      </c>
+      <c r="B132" t="str">
+        <v>1/31/2026, 9:18:38 PM</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>0194</v>
+      </c>
+      <c r="B133" t="str">
+        <v>1/31/2026, 9:19:38 PM</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>0193</v>
+      </c>
+      <c r="B134" t="str">
+        <v>1/31/2026, 9:20:38 PM</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>0193</v>
+      </c>
+      <c r="B135" t="str">
+        <v>1/31/2026, 9:20:38 PM</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>0101</v>
+      </c>
+      <c r="B136" t="str">
+        <v>1/31/2026, 9:21:38 PM</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>01</v>
+      </c>
+      <c r="B137" t="str">
+        <v>1/31/2026, 9:22:38 PM</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>1024148</v>
+      </c>
+      <c r="B138" t="str">
+        <v>1/31/2026, 9:23:38 PM</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>0185</v>
+      </c>
+      <c r="B139" t="str">
+        <v>1/31/2026, 9:24:38 PM</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>0193</v>
+      </c>
+      <c r="B140" t="str">
+        <v>1/31/2026, 9:25:38 PM</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B141" t="str">
+        <v>1/31/2026, 9:26:38 PM</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>0195</v>
+      </c>
+      <c r="B142" t="str">
+        <v>1/31/2026, 9:27:38 PM</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>0103</v>
+      </c>
+      <c r="B143" t="str">
+        <v>1/31/2026, 9:28:38 PM</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>0103</v>
+      </c>
+      <c r="B144" t="str">
+        <v>1/31/2026, 9:28:39 PM</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>01</v>
+      </c>
+      <c r="B145" t="str">
+        <v>1/31/2026, 9:29:38 PM</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>1024170</v>
+      </c>
+      <c r="B146" t="str">
+        <v>1/31/2026, 9:30:38 PM</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>0184</v>
+      </c>
+      <c r="B147" t="str">
+        <v>1/31/2026, 9:31:38 PM</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>0192</v>
+      </c>
+      <c r="B148" t="str">
+        <v>1/31/2026, 9:32:38 PM</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>0196</v>
+      </c>
+      <c r="B149" t="str">
+        <v>1/31/2026, 9:33:38 PM</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B150" t="str">
+        <v>1/31/2026, 9:34:38 PM</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B151" t="str">
+        <v>1/31/2026, 9:34:38 PM</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>0101</v>
+      </c>
+      <c r="B152" t="str">
+        <v>1/31/2026, 9:35:38 PM</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>01</v>
+      </c>
+      <c r="B153" t="str">
+        <v>1/31/2026, 9:36:38 PM</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>1024166</v>
+      </c>
+      <c r="B154" t="str">
+        <v>1/31/2026, 9:37:38 PM</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>1024166</v>
+      </c>
+      <c r="B155" t="str">
+        <v>1/31/2026, 9:37:38 PM</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>1024166</v>
+      </c>
+      <c r="B156" t="str">
+        <v>1/31/2026, 9:37:39 PM</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>1024166</v>
+      </c>
+      <c r="B157" t="str">
+        <v>1/31/2026, 9:37:39 PM</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>0179</v>
+      </c>
+      <c r="B158" t="str">
+        <v>1/31/2026, 9:38:38 PM</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B159" t="str">
+        <v>1/31/2026, 9:39:37 PM</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>0185</v>
+      </c>
+      <c r="B160" t="str">
+        <v>1/31/2026, 9:40:37 PM</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B161" t="str">
+        <v>1/31/2026, 9:41:37 PM</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>0191</v>
+      </c>
+      <c r="B162" t="str">
+        <v>1/31/2026, 9:41:37 PM</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>0186</v>
+      </c>
+      <c r="B163" t="str">
+        <v>1/31/2026, 9:57:43 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B163"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>0147</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2/2/2026, 4:16:49 PM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>0147</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2/2/2026, 4:16:49 PM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>0147</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2/2/2026, 4:16:49 PM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>0161</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2/2/2026, 4:17:48 PM</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>0161</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2/2/2026, 4:18:48 PM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>0157</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2/2/2026, 4:19:48 PM</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>091</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2/2/2026, 4:20:48 PM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>01</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2/2/2026, 4:21:48 PM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>061</v>
+      </c>
+      <c r="B2" t="str">
+        <v>3/17/2026, 4:01:56 PM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B33"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>016</v>
+      </c>
+      <c r="B2" t="str">
+        <v>4/14/2026, 5:00:22 PM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>015</v>
+      </c>
+      <c r="B3" t="str">
+        <v>4/14/2026, 5:19:22 PM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>017</v>
+      </c>
+      <c r="B4" t="str">
+        <v>4/14/2026, 5:20:22 PM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>016</v>
+      </c>
+      <c r="B5" t="str">
+        <v>4/14/2026, 5:21:22 PM</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>01</v>
+      </c>
+      <c r="B6" t="str">
+        <v>4/14/2026, 5:38:22 PM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>256156</v>
+      </c>
+      <c r="B7" t="str">
+        <v>4/14/2026, 5:39:22 PM</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>012</v>
+      </c>
+      <c r="B8" t="str">
+        <v>4/14/2026, 5:40:22 PM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>014</v>
+      </c>
+      <c r="B9" t="str">
+        <v>4/14/2026, 5:41:22 PM</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>014</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4/14/2026, 5:42:22 PM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>014</v>
+      </c>
+      <c r="B11" t="str">
+        <v>4/14/2026, 5:43:22 PM</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>028</v>
+      </c>
+      <c r="B12" t="str">
+        <v>4/14/2026, 6:44:22 PM</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4/14/2026, 6:45:23 PM</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>030</v>
+      </c>
+      <c r="B14" t="str">
+        <v>4/14/2026, 6:46:22 PM</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>0240</v>
+      </c>
+      <c r="B15" t="str">
+        <v>4/14/2026, 6:47:22 PM</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>256223</v>
+      </c>
+      <c r="B16" t="str">
+        <v>4/14/2026, 7:03:22 PM</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>023</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4/14/2026, 7:04:22 PM</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>0169</v>
+      </c>
+      <c r="B18" t="str">
+        <v>4/14/2026, 7:36:22 PM</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>01</v>
+      </c>
+      <c r="B19" t="str">
+        <v>4/14/2026, 7:37:22 PM</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>025</v>
+      </c>
+      <c r="B20" t="str">
+        <v>4/14/2026, 7:39:22 PM</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>025</v>
+      </c>
+      <c r="B21" t="str">
+        <v>4/14/2026, 7:39:22 PM</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>025</v>
+      </c>
+      <c r="B22" t="str">
+        <v>4/14/2026, 7:39:23 PM</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>029</v>
+      </c>
+      <c r="B23" t="str">
+        <v>4/14/2026, 7:40:25 PM</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>4/14/2026, 7:41:22 PM</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>028</v>
+      </c>
+      <c r="B25" t="str">
+        <v>4/14/2026, 7:42:22 PM</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>027</v>
+      </c>
+      <c r="B26" t="str">
+        <v>4/14/2026, 7:49:23 PM</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>01</v>
+      </c>
+      <c r="B27" t="str">
+        <v>4/14/2026, 7:51:22 PM</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>037</v>
+      </c>
+      <c r="B28" t="str">
+        <v>4/14/2026, 8:24:23 PM</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>077</v>
+      </c>
+      <c r="B29" t="str">
+        <v>4/14/2026, 8:25:23 PM</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>01</v>
+      </c>
+      <c r="B30" t="str">
+        <v>4/14/2026, 8:26:23 PM</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>256103</v>
+      </c>
+      <c r="B31" t="str">
+        <v>4/14/2026, 8:27:23 PM</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>4/14/2026, 8:28:23 PM</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>035</v>
+      </c>
+      <c r="B33" t="str">
+        <v>4/14/2026, 8:29:23 PM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B33"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>020</v>
+      </c>
+      <c r="B2" t="str">
+        <v>4/15/2026, 11:45:24 AM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>024</v>
+      </c>
+      <c r="B3" t="str">
+        <v>4/15/2026, 11:46:24 AM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>024</v>
+      </c>
+      <c r="B4" t="str">
+        <v>4/15/2026, 11:47:24 AM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>022</v>
+      </c>
+      <c r="B5" t="str">
+        <v>4/15/2026, 11:48:24 AM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B134"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Timestamp</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>51274</v>
+      </c>
+      <c r="B2" t="str">
+        <v>4/21/2026, 11:20:22 AM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>51274</v>
+      </c>
+      <c r="B3" t="str">
+        <v>4/21/2026, 11:20:23 AM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>08</v>
+      </c>
+      <c r="B4" t="str">
+        <v>4/21/2026, 11:21:22 AM</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>07</v>
+      </c>
+      <c r="B5" t="str">
+        <v>4/21/2026, 11:22:22 AM</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>07</v>
+      </c>
+      <c r="B6" t="str">
+        <v>4/21/2026, 11:23:22 AM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>09</v>
+      </c>
+      <c r="B7" t="str">
+        <v>4/21/2026, 11:24:22 AM</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>09</v>
+      </c>
+      <c r="B8" t="str">
+        <v>4/21/2026, 11:24:22 AM</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>0194</v>
+      </c>
+      <c r="B9" t="str">
+        <v>4/21/2026, 11:25:22 AM</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>0194</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4/21/2026, 11:25:23 AM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>0194</v>
+      </c>
+      <c r="B11" t="str">
+        <v>4/21/2026, 11:25:23 AM</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>01</v>
+      </c>
+      <c r="B12" t="str">
+        <v>4/21/2026, 11:26:23 AM</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>51269</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4/21/2026, 11:27:22 AM</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>08</v>
+      </c>
+      <c r="B14" t="str">
+        <v>4/21/2026, 11:28:22 AM</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>09</v>
+      </c>
+      <c r="B15" t="str">
+        <v>4/21/2026, 11:29:22 AM</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>09</v>
+      </c>
+      <c r="B16" t="str">
+        <v>4/21/2026, 11:29:22 AM</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>09</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4/21/2026, 11:29:23 AM</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>09</v>
+      </c>
+      <c r="B18" t="str">
+        <v>4/21/2026, 11:29:23 AM</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>09</v>
+      </c>
+      <c r="B19" t="str">
+        <v>4/21/2026, 11:30:23 AM</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>010</v>
+      </c>
+      <c r="B20" t="str">
+        <v>4/21/2026, 11:31:22 AM</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>0182</v>
+      </c>
+      <c r="B21" t="str">
+        <v>4/21/2026, 11:32:22 AM</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>01</v>
+      </c>
+      <c r="B22" t="str">
+        <v>4/21/2026, 11:33:23 AM</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>01</v>
+      </c>
+      <c r="B23" t="str">
+        <v>4/21/2026, 11:33:25 AM</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>51273</v>
+      </c>
+      <c r="B24" t="str">
+        <v>4/21/2026, 11:34:22 AM</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>08</v>
+      </c>
+      <c r="B25" t="str">
+        <v>4/21/2026, 11:35:23 AM</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>09</v>
+      </c>
+      <c r="B26" t="str">
+        <v>4/21/2026, 11:36:22 AM</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>09</v>
+      </c>
+      <c r="B27" t="str">
+        <v>4/21/2026, 11:37:23 AM</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>09</v>
+      </c>
+      <c r="B28" t="str">
+        <v>4/21/2026, 11:38:23 AM</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>0149</v>
+      </c>
+      <c r="B29" t="str">
+        <v>4/21/2026, 11:39:22 AM</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>0149</v>
+      </c>
+      <c r="B30" t="str">
+        <v>4/21/2026, 11:39:22 AM</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>01</v>
+      </c>
+      <c r="B31" t="str">
+        <v>4/21/2026, 11:40:22 AM</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>01</v>
+      </c>
+      <c r="B32" t="str">
+        <v>4/21/2026, 11:40:23 AM</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>51274</v>
+      </c>
+      <c r="B33" t="str">
+        <v>4/21/2026, 11:41:22 AM</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>09</v>
+      </c>
+      <c r="B34" t="str">
+        <v>4/21/2026, 11:42:22 AM</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>09</v>
+      </c>
+      <c r="B35" t="str">
+        <v>4/21/2026, 11:42:22 AM</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>08</v>
+      </c>
+      <c r="B36" t="str">
+        <v>4/21/2026, 11:43:22 AM</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>08</v>
+      </c>
+      <c r="B37" t="str">
+        <v>4/21/2026, 11:43:23 AM</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>09</v>
+      </c>
+      <c r="B38" t="str">
+        <v>4/21/2026, 11:44:22 AM</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>011</v>
+      </c>
+      <c r="B39" t="str">
+        <v>4/21/2026, 11:45:23 AM</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>0107</v>
+      </c>
+      <c r="B40" t="str">
+        <v>4/21/2026, 11:46:22 AM</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>01</v>
+      </c>
+      <c r="B41" t="str">
+        <v>4/21/2026, 11:47:22 AM</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>08</v>
+      </c>
+      <c r="B42" t="str">
+        <v>4/21/2026, 11:49:22 AM</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>08</v>
+      </c>
+      <c r="B43" t="str">
+        <v>4/21/2026, 11:50:22 AM</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>09</v>
+      </c>
+      <c r="B44" t="str">
+        <v>4/21/2026, 11:51:22 AM</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>08</v>
+      </c>
+      <c r="B45" t="str">
+        <v>4/21/2026, 11:52:22 AM</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>0102</v>
+      </c>
+      <c r="B46" t="str">
+        <v>4/21/2026, 11:53:22 AM</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>01</v>
+      </c>
+      <c r="B47" t="str">
+        <v>4/21/2026, 11:54:22 AM</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>01</v>
+      </c>
+      <c r="B48" t="str">
+        <v>4/21/2026, 11:54:57 AM</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>51274</v>
+      </c>
+      <c r="B49" t="str">
+        <v>4/21/2026, 11:55:22 AM</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>08</v>
+      </c>
+      <c r="B50" t="str">
+        <v>4/21/2026, 11:56:22 AM</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>09</v>
+      </c>
+      <c r="B51" t="str">
+        <v>4/21/2026, 11:57:22 AM</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>09</v>
+      </c>
+      <c r="B52" t="str">
+        <v>4/21/2026, 11:58:22 AM</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>09</v>
+      </c>
+      <c r="B53" t="str">
+        <v>4/21/2026, 11:58:23 AM</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>09</v>
+      </c>
+      <c r="B54" t="str">
+        <v>4/21/2026, 11:59:22 AM</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>064</v>
+      </c>
+      <c r="B55" t="str">
+        <v>4/21/2026, 12:00:22 PM</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>01</v>
+      </c>
+      <c r="B56" t="str">
+        <v>4/21/2026, 12:01:23 PM</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>51268</v>
+      </c>
+      <c r="B57" t="str">
+        <v>4/21/2026, 12:02:22 PM</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>51268</v>
+      </c>
+      <c r="B58" t="str">
+        <v>4/21/2026, 12:02:23 PM</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>08</v>
+      </c>
+      <c r="B59" t="str">
+        <v>4/21/2026, 12:03:23 PM</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>08</v>
+      </c>
+      <c r="B60" t="str">
+        <v>4/21/2026, 12:04:23 PM</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>08</v>
+      </c>
+      <c r="B61" t="str">
+        <v>4/21/2026, 12:05:22 PM</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>08</v>
+      </c>
+      <c r="B62" t="str">
+        <v>4/21/2026, 12:06:22 PM</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>045</v>
+      </c>
+      <c r="B63" t="str">
+        <v>4/21/2026, 12:07:22 PM</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>01</v>
+      </c>
+      <c r="B64" t="str">
+        <v>4/21/2026, 12:08:22 PM</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>01</v>
+      </c>
+      <c r="B65" t="str">
+        <v>4/21/2026, 12:08:23 PM</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>01</v>
+      </c>
+      <c r="B66" t="str">
+        <v>4/21/2026, 12:08:23 PM</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>51272</v>
+      </c>
+      <c r="B67" t="str">
+        <v>4/21/2026, 12:09:22 PM</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>08</v>
+      </c>
+      <c r="B68" t="str">
+        <v>4/21/2026, 12:10:22 PM</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>08</v>
+      </c>
+      <c r="B69" t="str">
+        <v>4/21/2026, 12:10:23 PM</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>08</v>
+      </c>
+      <c r="B70" t="str">
+        <v>4/21/2026, 12:11:22 PM</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>08</v>
+      </c>
+      <c r="B71" t="str">
+        <v>4/21/2026, 12:12:22 PM</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>08</v>
+      </c>
+      <c r="B72" t="str">
+        <v>4/21/2026, 12:13:22 PM</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>01</v>
+      </c>
+      <c r="B73" t="str">
+        <v>4/21/2026, 12:15:22 PM</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>51265</v>
+      </c>
+      <c r="B74" t="str">
+        <v>4/21/2026, 12:16:23 PM</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>07</v>
+      </c>
+      <c r="B75" t="str">
+        <v>4/21/2026, 12:17:22 PM</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>08</v>
+      </c>
+      <c r="B76" t="str">
+        <v>4/21/2026, 12:18:22 PM</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>08</v>
+      </c>
+      <c r="B77" t="str">
+        <v>4/21/2026, 12:18:23 PM</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>08</v>
+      </c>
+      <c r="B78" t="str">
+        <v>4/21/2026, 12:19:22 PM</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>08</v>
+      </c>
+      <c r="B79" t="str">
+        <v>4/21/2026, 12:19:23 PM</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>07</v>
+      </c>
+      <c r="B80" t="str">
+        <v>4/21/2026, 12:20:22 PM</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>032</v>
+      </c>
+      <c r="B81" t="str">
+        <v>4/21/2026, 12:21:22 PM</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>01</v>
+      </c>
+      <c r="B82" t="str">
+        <v>4/21/2026, 12:22:22 PM</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>01</v>
+      </c>
+      <c r="B83" t="str">
+        <v>4/21/2026, 12:22:23 PM</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>51263</v>
+      </c>
+      <c r="B84" t="str">
+        <v>4/21/2026, 12:23:22 PM</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>05</v>
+      </c>
+      <c r="B85" t="str">
+        <v>4/21/2026, 12:24:22 PM</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>05</v>
+      </c>
+      <c r="B86" t="str">
+        <v>4/21/2026, 12:25:32 PM</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>06</v>
+      </c>
+      <c r="B87" t="str">
+        <v>4/21/2026, 1:30:23 PM</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>06</v>
+      </c>
+      <c r="B88" t="str">
+        <v>4/21/2026, 1:30:23 PM</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>088</v>
+      </c>
+      <c r="B89" t="str">
+        <v>4/21/2026, 1:31:23 PM</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>01</v>
+      </c>
+      <c r="B90" t="str">
+        <v>4/21/2026, 1:32:22 PM</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>01</v>
+      </c>
+      <c r="B91" t="str">
+        <v>4/21/2026, 1:32:23 PM</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>01</v>
+      </c>
+      <c r="B92" t="str">
+        <v>4/21/2026, 1:32:23 PM</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>51279</v>
+      </c>
+      <c r="B93" t="str">
+        <v>4/21/2026, 1:33:22 PM</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>00</v>
+      </c>
+      <c r="B94" t="str">
+        <v>4/21/2026, 1:34:22 PM</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>00</v>
+      </c>
+      <c r="B95" t="str">
+        <v>4/21/2026, 1:35:23 PM</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>00</v>
+      </c>
+      <c r="B96" t="str">
+        <v>4/21/2026, 1:35:23 PM</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>00</v>
+      </c>
+      <c r="B97" t="str">
+        <v>4/21/2026, 1:35:23 PM</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>00</v>
+      </c>
+      <c r="B98" t="str">
+        <v>4/21/2026, 1:36:23 PM</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>00</v>
+      </c>
+      <c r="B99" t="str">
+        <v>4/21/2026, 1:37:23 PM</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>256124</v>
+      </c>
+      <c r="B100" t="str">
+        <v>4/21/2026, 1:38:25 PM</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>256124</v>
+      </c>
+      <c r="B101" t="str">
+        <v>4/21/2026, 1:38:25 PM</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>256124</v>
+      </c>
+      <c r="B102" t="str">
+        <v>4/21/2026, 1:38:25 PM</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>01</v>
+      </c>
+      <c r="B103" t="str">
+        <v>4/21/2026, 1:39:22 PM</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>51269</v>
+      </c>
+      <c r="B104" t="str">
+        <v>4/21/2026, 1:40:22 PM</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>00</v>
+      </c>
+      <c r="B105" t="str">
+        <v>4/21/2026, 1:41:22 PM</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>00</v>
+      </c>
+      <c r="B106" t="str">
+        <v>4/21/2026, 1:43:23 PM</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>00</v>
+      </c>
+      <c r="B107" t="str">
+        <v>4/21/2026, 1:44:22 PM</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>00</v>
+      </c>
+      <c r="B108" t="str">
+        <v>4/21/2026, 1:44:23 PM</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>256176</v>
+      </c>
+      <c r="B109" t="str">
+        <v>4/21/2026, 1:45:32 PM</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>01</v>
+      </c>
+      <c r="B110" t="str">
+        <v>4/21/2026, 1:46:23 PM</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>51262</v>
+      </c>
+      <c r="B111" t="str">
+        <v>4/21/2026, 1:47:22 PM</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>00</v>
+      </c>
+      <c r="B112" t="str">
+        <v>4/21/2026, 1:48:23 PM</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>024</v>
+      </c>
+      <c r="B113" t="str">
+        <v>4/21/2026, 7:48:14 PM</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>024</v>
+      </c>
+      <c r="B114" t="str">
+        <v>4/21/2026, 7:49:14 PM</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>0171</v>
+      </c>
+      <c r="B115" t="str">
+        <v>4/21/2026, 7:50:14 PM</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>02</v>
+      </c>
+      <c r="B116" t="str">
+        <v>4/21/2026, 7:51:14 PM</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>512177</v>
+      </c>
+      <c r="B117" t="str">
+        <v>4/21/2026, 7:52:14 PM</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>512177</v>
+      </c>
+      <c r="B118" t="str">
+        <v>4/21/2026, 7:52:14 PM</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>025</v>
+      </c>
+      <c r="B119" t="str">
+        <v>4/21/2026, 7:53:14 PM</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>027</v>
+      </c>
+      <c r="B120" t="str">
+        <v>4/21/2026, 7:54:14 PM</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>027</v>
+      </c>
+      <c r="B121" t="str">
+        <v>4/21/2026, 7:54:14 PM</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>027</v>
+      </c>
+      <c r="B122" t="str">
+        <v>4/21/2026, 7:55:14 PM</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>030</v>
+      </c>
+      <c r="B123" t="str">
+        <v>4/21/2026, 7:56:14 PM</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>031</v>
+      </c>
+      <c r="B124" t="str">
+        <v>4/21/2026, 8:09:19 PM</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>032</v>
+      </c>
+      <c r="B125" t="str">
+        <v>4/21/2026, 8:10:14 PM</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>055</v>
+      </c>
+      <c r="B126" t="str">
+        <v>4/21/2026, 8:11:14 PM</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>03</v>
+      </c>
+      <c r="B127" t="str">
+        <v>4/21/2026, 8:12:15 PM</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>038</v>
+      </c>
+      <c r="B128" t="str">
+        <v>4/21/2026, 8:23:14 PM</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>036</v>
+      </c>
+      <c r="B129" t="str">
+        <v>4/21/2026, 8:24:14 PM</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>055</v>
+      </c>
+      <c r="B130" t="str">
+        <v>4/21/2026, 8:25:14 PM</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>03</v>
+      </c>
+      <c r="B131" t="str">
+        <v>4/21/2026, 8:26:14 PM</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>00</v>
+      </c>
+      <c r="B132" t="str">
+        <v>4/21/2026, 8:27:14 PM</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>00</v>
+      </c>
+      <c r="B133" t="str">
+        <v>4/21/2026, 8:27:15 PM</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>037</v>
+      </c>
+      <c r="B134" t="str">
+        <v>4/21/2026, 8:28:16 PM</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B134"/>
   </ignoredErrors>
 </worksheet>
 </file>